--- a/publication_database.xlsx
+++ b/publication_database.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB2C539-1BF1-4A0F-8A07-D69B357CAB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13055"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -55,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="659">
   <si>
     <t>Type</t>
   </si>
@@ -447,7 +453,7 @@
         <sz val="11"/>
         <color rgb="FF1F1F1F"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -465,7 +471,7 @@
         <sz val="11"/>
         <color rgb="FF1F1F1F"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -494,7 +500,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>VMD</t>
     </r>
@@ -520,7 +526,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Systems Engineering </t>
     </r>
@@ -538,7 +544,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Theory &amp; Practice</t>
     </r>
@@ -564,7 +570,7 @@
         <sz val="11"/>
         <color rgb="FF1F1F1F"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -582,7 +588,7 @@
         <sz val="11"/>
         <color rgb="FF1F1F1F"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -600,7 +606,7 @@
         <sz val="11"/>
         <color rgb="FF1F1F1F"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>;</t>
     </r>
@@ -618,7 +624,7 @@
         <sz val="11"/>
         <color rgb="FF1F1F1F"/>
         <rFont val="Arial"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -659,7 +665,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>;</t>
     </r>
@@ -677,7 +683,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>;</t>
     </r>
@@ -695,7 +701,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>;</t>
     </r>
@@ -713,7 +719,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>;</t>
     </r>
@@ -751,7 +757,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>;</t>
     </r>
@@ -769,7 +775,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>;</t>
     </r>
@@ -801,7 +807,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>GAF-CNN-Transformer</t>
     </r>
@@ -1141,7 +1147,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>A stability analysis for the online retailing cyber security situation piecewise variable weight</t>
     </r>
@@ -1159,7 +1165,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>rating method</t>
     </r>
@@ -1380,7 +1386,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -1595,7 +1601,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -1613,7 +1619,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -1631,7 +1637,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -1649,7 +1655,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -1667,7 +1673,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -1685,7 +1691,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -1703,7 +1709,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -1721,7 +1727,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -1990,7 +1996,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2434,7 +2440,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -2570,7 +2576,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">; </t>
     </r>
@@ -2685,18 +2691,16 @@
   <si>
     <t>Hong Kong, China</t>
   </si>
+  <si>
+    <t>1213-1243</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2713,13 +2717,13 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2735,157 +2739,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2894,10 +2747,22 @@
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2922,194 +2787,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -3117,254 +2796,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3423,60 +2860,15 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font>
         <strike val="0"/>
@@ -3484,6 +2876,26 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3503,16 +2915,6 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor theme="2"/>
         </patternFill>
       </fill>
@@ -3523,12 +2925,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Category_Quartiles"/>
@@ -3827,33 +3232,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF114"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="79.8" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="79.8" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="3" customWidth="1"/>
-    <col min="2" max="4" width="9.33333333333333" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19.1111111111111" style="3" customWidth="1"/>
-    <col min="6" max="6" width="27.4444444444444" style="3" customWidth="1"/>
-    <col min="7" max="7" width="8.88888888888889" style="4"/>
-    <col min="8" max="8" width="24.3333333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="30.6666666666667" style="3" customWidth="1"/>
-    <col min="10" max="10" width="8.88888888888889" style="3"/>
-    <col min="11" max="11" width="10.8888888888889" style="3" customWidth="1"/>
-    <col min="12" max="13" width="16.7777777777778" style="3" customWidth="1"/>
-    <col min="14" max="16" width="8.88888888888889" style="3"/>
-    <col min="17" max="17" width="24.5555555555556" style="5" customWidth="1"/>
-    <col min="18" max="24" width="8.88888888888889" style="3"/>
-    <col min="25" max="25" width="8.88888888888889" style="4"/>
-    <col min="26" max="16384" width="8.88888888888889" style="3"/>
+    <col min="1" max="1" width="8.88671875" style="3" customWidth="1"/>
+    <col min="2" max="4" width="9.33203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="27.44140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+    <col min="8" max="8" width="24.33203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="30.6640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="3"/>
+    <col min="11" max="11" width="10.88671875" style="3" customWidth="1"/>
+    <col min="12" max="13" width="16.77734375" style="3" customWidth="1"/>
+    <col min="14" max="16" width="8.88671875" style="3"/>
+    <col min="17" max="17" width="24.5546875" style="5" customWidth="1"/>
+    <col min="18" max="24" width="8.88671875" style="3"/>
+    <col min="25" max="25" width="8.88671875" style="4"/>
+    <col min="26" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:32">
+    <row r="1" spans="1:32" s="1" customFormat="1" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3951,7 +3356,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:32">
+    <row r="2" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
@@ -3970,7 +3375,7 @@
       <c r="F2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="6"/>
+      <c r="G2" s="8"/>
       <c r="H2" s="7" t="s">
         <v>36</v>
       </c>
@@ -3989,13 +3394,13 @@
       <c r="M2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="8" t="str" cm="1">
         <f t="array" ref="R2">_xlfn.LET(_xlpm.issn,TRIM(M2),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>6.9</v>
+        <v/>
       </c>
       <c r="S2" s="8" t="s">
         <v>39</v>
@@ -4022,7 +3427,7 @@
       <c r="AE2" s="8"/>
       <c r="AF2" s="8"/>
     </row>
-    <row r="3" s="2" customFormat="1" customHeight="1" spans="1:32">
+    <row r="3" spans="1:32" s="2" customFormat="1" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>32</v>
       </c>
@@ -4041,7 +3446,7 @@
       <c r="F3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="10"/>
+      <c r="G3" s="11"/>
       <c r="H3" s="10" t="s">
         <v>42</v>
       </c>
@@ -4060,13 +3465,13 @@
       <c r="M3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="8" t="str" cm="1">
         <f t="array" ref="R3">_xlfn.LET(_xlpm.issn,TRIM(M3),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.0</v>
+        <v/>
       </c>
       <c r="S3" s="11" t="s">
         <v>39</v>
@@ -4091,7 +3496,7 @@
       <c r="AE3" s="11"/>
       <c r="AF3" s="11"/>
     </row>
-    <row r="4" customHeight="1" spans="1:32">
+    <row r="4" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>32</v>
       </c>
@@ -4110,7 +3515,7 @@
       <c r="F4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="8"/>
       <c r="H4" s="6" t="s">
         <v>49</v>
       </c>
@@ -4129,13 +3534,13 @@
       <c r="M4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="8" t="str" cm="1">
         <f t="array" ref="R4">_xlfn.LET(_xlpm.issn,TRIM(M4),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>6.9</v>
+        <v/>
       </c>
       <c r="S4" s="8" t="s">
         <v>39</v>
@@ -4162,7 +3567,7 @@
       <c r="AE4" s="8"/>
       <c r="AF4" s="8"/>
     </row>
-    <row r="5" customHeight="1" spans="1:32">
+    <row r="5" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>32</v>
       </c>
@@ -4181,7 +3586,7 @@
       <c r="F5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="6"/>
+      <c r="G5" s="8"/>
       <c r="H5" s="7" t="s">
         <v>52</v>
       </c>
@@ -4200,13 +3605,13 @@
       <c r="M5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="8" t="str" cm="1">
         <f t="array" ref="R5">_xlfn.LET(_xlpm.issn,TRIM(M5),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>14.5</v>
+        <v/>
       </c>
       <c r="S5" s="8"/>
       <c r="T5" s="12" t="s">
@@ -4229,7 +3634,7 @@
       <c r="AE5" s="8"/>
       <c r="AF5" s="8"/>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:32">
+    <row r="6" spans="1:32" s="2" customFormat="1" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>32</v>
       </c>
@@ -4248,7 +3653,7 @@
       <c r="F6" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="11"/>
       <c r="H6" s="13" t="s">
         <v>55</v>
       </c>
@@ -4267,13 +3672,13 @@
       <c r="M6" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="8" t="str" cm="1">
         <f t="array" ref="R6">_xlfn.LET(_xlpm.issn,TRIM(M6),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>5.0</v>
+        <v/>
       </c>
       <c r="S6" s="11"/>
       <c r="T6" s="11" t="s">
@@ -4296,7 +3701,7 @@
       <c r="AE6" s="11"/>
       <c r="AF6" s="11"/>
     </row>
-    <row r="7" customHeight="1" spans="1:32">
+    <row r="7" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>32</v>
       </c>
@@ -4315,7 +3720,7 @@
       <c r="F7" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="6"/>
+      <c r="G7" s="8"/>
       <c r="H7" s="6" t="s">
         <v>58</v>
       </c>
@@ -4334,13 +3739,13 @@
       <c r="M7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="8" t="str" cm="1">
         <f t="array" ref="R7">_xlfn.LET(_xlpm.issn,TRIM(M7),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>6.2</v>
+        <v/>
       </c>
       <c r="S7" s="8" t="s">
         <v>39</v>
@@ -4365,7 +3770,7 @@
       <c r="AE7" s="8"/>
       <c r="AF7" s="8"/>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:32">
+    <row r="8" spans="1:32" s="2" customFormat="1" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>32</v>
       </c>
@@ -4384,7 +3789,7 @@
       <c r="F8" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="10"/>
+      <c r="G8" s="11"/>
       <c r="H8" s="10" t="s">
         <v>62</v>
       </c>
@@ -4402,13 +3807,13 @@
       <c r="M8" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="8" t="str" cm="1">
         <f t="array" ref="R8">_xlfn.LET(_xlpm.issn,TRIM(M8),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>9.7</v>
+        <v/>
       </c>
       <c r="S8" s="11" t="s">
         <v>39</v>
@@ -4429,7 +3834,7 @@
       <c r="AE8" s="11"/>
       <c r="AF8" s="11"/>
     </row>
-    <row r="9" customHeight="1" spans="1:32">
+    <row r="9" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>32</v>
       </c>
@@ -4448,7 +3853,7 @@
       <c r="F9" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="G9" s="8"/>
       <c r="H9" s="7" t="s">
         <v>66</v>
       </c>
@@ -4467,13 +3872,13 @@
       <c r="M9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
       <c r="Q9" s="6"/>
       <c r="R9" s="8" t="str" cm="1">
         <f t="array" ref="R9">_xlfn.LET(_xlpm.issn,TRIM(M9),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>8.4</v>
+        <v/>
       </c>
       <c r="S9" s="8" t="s">
         <v>39</v>
@@ -4498,7 +3903,7 @@
       <c r="AE9" s="8"/>
       <c r="AF9" s="8"/>
     </row>
-    <row r="10" customHeight="1" spans="1:32">
+    <row r="10" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>32</v>
       </c>
@@ -4517,7 +3922,7 @@
       <c r="F10" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="15"/>
+      <c r="G10" s="16"/>
       <c r="H10" s="15" t="s">
         <v>71</v>
       </c>
@@ -4536,13 +3941,13 @@
       <c r="M10" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
       <c r="Q10" s="15"/>
       <c r="R10" s="8" t="str" cm="1">
         <f t="array" ref="R10">_xlfn.LET(_xlpm.issn,TRIM(M10),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>2.6</v>
+        <v/>
       </c>
       <c r="S10" s="16" t="s">
         <v>39</v>
@@ -4569,7 +3974,7 @@
       <c r="AE10" s="16"/>
       <c r="AF10" s="16"/>
     </row>
-    <row r="11" customHeight="1" spans="1:32">
+    <row r="11" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>32</v>
       </c>
@@ -4588,7 +3993,7 @@
       <c r="F11" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="6"/>
+      <c r="G11" s="8"/>
       <c r="H11" s="6" t="s">
         <v>74</v>
       </c>
@@ -4607,13 +4012,13 @@
       <c r="M11" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
       <c r="Q11" s="6"/>
       <c r="R11" s="8" t="str" cm="1">
         <f t="array" ref="R11">_xlfn.LET(_xlpm.issn,TRIM(M11),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>11.3</v>
+        <v/>
       </c>
       <c r="S11" s="8" t="s">
         <v>39</v>
@@ -4638,7 +4043,7 @@
       <c r="AE11" s="8"/>
       <c r="AF11" s="8"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:32">
+    <row r="12" spans="1:32" s="2" customFormat="1" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>32</v>
       </c>
@@ -4657,7 +4062,7 @@
       <c r="F12" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="10"/>
+      <c r="G12" s="11"/>
       <c r="H12" s="10" t="s">
         <v>77</v>
       </c>
@@ -4676,13 +4081,13 @@
       <c r="M12" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
       <c r="Q12" s="10"/>
       <c r="R12" s="8" t="str" cm="1">
         <f t="array" ref="R12">_xlfn.LET(_xlpm.issn,TRIM(M12),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.6</v>
+        <v/>
       </c>
       <c r="S12" s="11" t="s">
         <v>39</v>
@@ -4707,7 +4112,7 @@
       <c r="AE12" s="11"/>
       <c r="AF12" s="11"/>
     </row>
-    <row r="13" customHeight="1" spans="1:32">
+    <row r="13" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>32</v>
       </c>
@@ -4726,7 +4131,7 @@
       <c r="F13" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="8"/>
       <c r="H13" s="6" t="s">
         <v>82</v>
       </c>
@@ -4745,13 +4150,13 @@
       <c r="M13" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
       <c r="Q13" s="6"/>
       <c r="R13" s="8" t="str" cm="1">
         <f t="array" ref="R13">_xlfn.LET(_xlpm.issn,TRIM(M13),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>17.4</v>
+        <v/>
       </c>
       <c r="S13" s="8" t="s">
         <v>39</v>
@@ -4772,7 +4177,7 @@
       <c r="AE13" s="16"/>
       <c r="AF13" s="16"/>
     </row>
-    <row r="14" customHeight="1" spans="1:32">
+    <row r="14" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>32</v>
       </c>
@@ -4791,7 +4196,7 @@
       <c r="F14" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="15"/>
+      <c r="G14" s="16"/>
       <c r="H14" s="17" t="s">
         <v>86</v>
       </c>
@@ -4810,13 +4215,13 @@
       <c r="M14" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
       <c r="Q14" s="15"/>
       <c r="R14" s="8" t="str" cm="1">
         <f t="array" ref="R14">_xlfn.LET(_xlpm.issn,TRIM(M14),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.8</v>
+        <v/>
       </c>
       <c r="S14" s="18" t="s">
         <v>39</v>
@@ -4837,7 +4242,7 @@
       <c r="AE14" s="16"/>
       <c r="AF14" s="16"/>
     </row>
-    <row r="15" customHeight="1" spans="1:32">
+    <row r="15" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
         <v>32</v>
       </c>
@@ -4856,7 +4261,7 @@
       <c r="F15" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="G15" s="6"/>
+      <c r="G15" s="8"/>
       <c r="H15" s="7" t="s">
         <v>91</v>
       </c>
@@ -4875,13 +4280,13 @@
       <c r="M15" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
       <c r="Q15" s="6"/>
       <c r="R15" s="8" t="str" cm="1">
         <f t="array" ref="R15">_xlfn.LET(_xlpm.issn,TRIM(M15),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>8.1</v>
+        <v/>
       </c>
       <c r="S15" s="8" t="s">
         <v>39</v>
@@ -4906,7 +4311,7 @@
       <c r="AE15" s="8"/>
       <c r="AF15" s="8"/>
     </row>
-    <row r="16" customHeight="1" spans="1:32">
+    <row r="16" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>32</v>
       </c>
@@ -4925,7 +4330,7 @@
       <c r="F16" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="15"/>
+      <c r="G16" s="16"/>
       <c r="H16" s="17" t="s">
         <v>95</v>
       </c>
@@ -4944,13 +4349,13 @@
       <c r="M16" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
       <c r="Q16" s="15"/>
       <c r="R16" s="8" t="str" cm="1">
         <f t="array" ref="R16">_xlfn.LET(_xlpm.issn,TRIM(M16),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>9.4</v>
+        <v/>
       </c>
       <c r="S16" s="16" t="s">
         <v>39</v>
@@ -4971,7 +4376,7 @@
       <c r="AE16" s="16"/>
       <c r="AF16" s="16"/>
     </row>
-    <row r="17" customHeight="1" spans="1:32">
+    <row r="17" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>32</v>
       </c>
@@ -4990,7 +4395,7 @@
       <c r="F17" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G17" s="6"/>
+      <c r="G17" s="8"/>
       <c r="H17" s="6" t="s">
         <v>99</v>
       </c>
@@ -5009,13 +4414,13 @@
       <c r="M17" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
       <c r="Q17" s="6"/>
       <c r="R17" s="8" t="str" cm="1">
         <f t="array" ref="R17">_xlfn.LET(_xlpm.issn,TRIM(M17),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.3</v>
+        <v/>
       </c>
       <c r="S17" s="8" t="s">
         <v>39</v>
@@ -5040,7 +4445,7 @@
       <c r="AE17" s="8"/>
       <c r="AF17" s="8"/>
     </row>
-    <row r="18" customHeight="1" spans="1:32">
+    <row r="18" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>32</v>
       </c>
@@ -5059,7 +4464,7 @@
       <c r="F18" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="G18" s="15"/>
+      <c r="G18" s="16"/>
       <c r="H18" s="15" t="s">
         <v>104</v>
       </c>
@@ -5078,13 +4483,13 @@
       <c r="M18" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
       <c r="Q18" s="15"/>
       <c r="R18" s="8" t="str" cm="1">
         <f t="array" ref="R18">_xlfn.LET(_xlpm.issn,TRIM(M18),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.8</v>
+        <v/>
       </c>
       <c r="S18" s="16" t="s">
         <v>39</v>
@@ -5105,7 +4510,7 @@
       <c r="AE18" s="16"/>
       <c r="AF18" s="16"/>
     </row>
-    <row r="19" customHeight="1" spans="1:32">
+    <row r="19" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>32</v>
       </c>
@@ -5124,7 +4529,7 @@
       <c r="F19" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="6"/>
+      <c r="G19" s="8"/>
       <c r="H19" s="6" t="s">
         <v>107</v>
       </c>
@@ -5143,13 +4548,13 @@
       <c r="M19" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
       <c r="Q19" s="6"/>
       <c r="R19" s="8" t="str" cm="1">
         <f t="array" ref="R19">_xlfn.LET(_xlpm.issn,TRIM(M19),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>9.4</v>
+        <v/>
       </c>
       <c r="S19" s="8" t="s">
         <v>39</v>
@@ -5170,7 +4575,7 @@
       <c r="AE19" s="8"/>
       <c r="AF19" s="8"/>
     </row>
-    <row r="20" customHeight="1" spans="1:32">
+    <row r="20" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>32</v>
       </c>
@@ -5189,7 +4594,7 @@
       <c r="F20" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G20" s="15"/>
+      <c r="G20" s="16"/>
       <c r="H20" s="17" t="s">
         <v>109</v>
       </c>
@@ -5208,13 +4613,13 @@
       <c r="M20" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
       <c r="Q20" s="15"/>
       <c r="R20" s="8" t="str" cm="1">
         <f t="array" ref="R20">_xlfn.LET(_xlpm.issn,TRIM(M20),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>2.6</v>
+        <v/>
       </c>
       <c r="S20" s="16" t="s">
         <v>39</v>
@@ -5241,7 +4646,7 @@
       <c r="AE20" s="16"/>
       <c r="AF20" s="16"/>
     </row>
-    <row r="21" customHeight="1" spans="1:32">
+    <row r="21" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>32</v>
       </c>
@@ -5260,7 +4665,7 @@
       <c r="F21" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="6"/>
+      <c r="G21" s="8"/>
       <c r="H21" s="7" t="s">
         <v>110</v>
       </c>
@@ -5280,13 +4685,13 @@
       <c r="M21" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
       <c r="Q21" s="6"/>
       <c r="R21" s="8" t="str" cm="1">
         <f t="array" ref="R21">_xlfn.LET(_xlpm.issn,TRIM(M21),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>6.0</v>
+        <v/>
       </c>
       <c r="S21" s="8" t="s">
         <v>39</v>
@@ -5309,7 +4714,7 @@
       <c r="AE21" s="8"/>
       <c r="AF21" s="8"/>
     </row>
-    <row r="22" customHeight="1" spans="1:32">
+    <row r="22" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>32</v>
       </c>
@@ -5328,7 +4733,7 @@
       <c r="F22" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="G22" s="15"/>
+      <c r="G22" s="16"/>
       <c r="H22" s="17" t="s">
         <v>115</v>
       </c>
@@ -5347,13 +4752,13 @@
       <c r="M22" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
       <c r="Q22" s="15"/>
       <c r="R22" s="8" t="str" cm="1">
         <f t="array" ref="R22">_xlfn.LET(_xlpm.issn,TRIM(M22),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>17.4</v>
+        <v/>
       </c>
       <c r="S22" s="16" t="s">
         <v>39</v>
@@ -5374,7 +4779,7 @@
       <c r="AE22" s="16"/>
       <c r="AF22" s="16"/>
     </row>
-    <row r="23" customHeight="1" spans="1:32">
+    <row r="23" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>32</v>
       </c>
@@ -5393,7 +4798,7 @@
       <c r="F23" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="G23" s="15"/>
+      <c r="G23" s="16"/>
       <c r="H23" s="15" t="s">
         <v>120</v>
       </c>
@@ -5408,9 +4813,9 @@
         <v>123</v>
       </c>
       <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
       <c r="Q23" s="15"/>
       <c r="R23" s="8" t="str" cm="1">
         <f t="array" ref="R23">_xlfn.LET(_xlpm.issn,TRIM(M23),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
@@ -5435,7 +4840,7 @@
       <c r="AE23" s="16"/>
       <c r="AF23" s="16"/>
     </row>
-    <row r="24" customHeight="1" spans="1:32">
+    <row r="24" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>32</v>
       </c>
@@ -5454,7 +4859,7 @@
       <c r="F24" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="6"/>
+      <c r="G24" s="8"/>
       <c r="H24" s="6" t="s">
         <v>126</v>
       </c>
@@ -5469,9 +4874,9 @@
         <v>129</v>
       </c>
       <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
       <c r="Q24" s="6"/>
       <c r="R24" s="8" t="str" cm="1">
         <f t="array" ref="R24">_xlfn.LET(_xlpm.issn,TRIM(M24),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
@@ -5498,7 +4903,7 @@
       <c r="AE24" s="8"/>
       <c r="AF24" s="8"/>
     </row>
-    <row r="25" customHeight="1" spans="1:32">
+    <row r="25" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>32</v>
       </c>
@@ -5517,7 +4922,7 @@
       <c r="F25" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="G25" s="15"/>
+      <c r="G25" s="16"/>
       <c r="H25" s="15" t="s">
         <v>134</v>
       </c>
@@ -5532,9 +4937,9 @@
         <v>136</v>
       </c>
       <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
       <c r="Q25" s="15"/>
       <c r="R25" s="8" t="str" cm="1">
         <f t="array" ref="R25">_xlfn.LET(_xlpm.issn,TRIM(M25),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
@@ -5561,7 +4966,7 @@
       <c r="AE25" s="16"/>
       <c r="AF25" s="16"/>
     </row>
-    <row r="26" customHeight="1" spans="1:32">
+    <row r="26" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>32</v>
       </c>
@@ -5580,7 +4985,7 @@
       <c r="F26" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="G26" s="6"/>
+      <c r="G26" s="8"/>
       <c r="H26" s="6" t="s">
         <v>139</v>
       </c>
@@ -5595,9 +5000,9 @@
         <v>123</v>
       </c>
       <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
       <c r="Q26" s="6"/>
       <c r="R26" s="8" t="str" cm="1">
         <f t="array" ref="R26">_xlfn.LET(_xlpm.issn,TRIM(M26),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
@@ -5622,7 +5027,7 @@
       <c r="AE26" s="8"/>
       <c r="AF26" s="8"/>
     </row>
-    <row r="27" customHeight="1" spans="1:32">
+    <row r="27" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>32</v>
       </c>
@@ -5641,7 +5046,7 @@
       <c r="F27" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="G27" s="15"/>
+      <c r="G27" s="16"/>
       <c r="H27" s="15" t="s">
         <v>143</v>
       </c>
@@ -5656,9 +5061,9 @@
         <v>123</v>
       </c>
       <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
       <c r="Q27" s="15"/>
       <c r="R27" s="8" t="str" cm="1">
         <f t="array" ref="R27">_xlfn.LET(_xlpm.issn,TRIM(M27),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
@@ -5683,7 +5088,7 @@
       <c r="AE27" s="16"/>
       <c r="AF27" s="16"/>
     </row>
-    <row r="28" customHeight="1" spans="1:32">
+    <row r="28" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>32</v>
       </c>
@@ -5702,12 +5107,12 @@
       <c r="F28" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="G28" s="6"/>
+      <c r="G28" s="8"/>
       <c r="H28" s="6" t="s">
         <v>146</v>
       </c>
       <c r="I28" s="6" t="str">
-        <f t="shared" ref="I28:I30" si="4">IF(B28="英文",H28,"")</f>
+        <f t="shared" ref="I28:I29" si="4">IF(B28="英文",H28,"")</f>
         <v>A linguistic distribution-based approach to support consensus reaching in MAGDM with multi-granular unbalanced hesitant fuzzy linguistic information</v>
       </c>
       <c r="J28" s="6"/>
@@ -5721,13 +5126,13 @@
       <c r="M28" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
       <c r="Q28" s="6"/>
       <c r="R28" s="8" t="str" cm="1">
         <f t="array" ref="R28">_xlfn.LET(_xlpm.issn,TRIM(M28),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.3</v>
+        <v/>
       </c>
       <c r="S28" s="8" t="s">
         <v>39</v>
@@ -5752,7 +5157,7 @@
       <c r="AE28" s="8"/>
       <c r="AF28" s="8"/>
     </row>
-    <row r="29" customHeight="1" spans="1:32">
+    <row r="29" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
         <v>32</v>
       </c>
@@ -5771,7 +5176,7 @@
       <c r="F29" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="G29" s="15"/>
+      <c r="G29" s="16"/>
       <c r="H29" s="15" t="s">
         <v>148</v>
       </c>
@@ -5790,13 +5195,13 @@
       <c r="M29" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="16"/>
       <c r="Q29" s="15"/>
       <c r="R29" s="8" t="str" cm="1">
         <f t="array" ref="R29">_xlfn.LET(_xlpm.issn,TRIM(M29),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>2.8</v>
+        <v/>
       </c>
       <c r="S29" s="16"/>
       <c r="T29" s="16" t="s">
@@ -5819,152 +5224,152 @@
       <c r="AE29" s="16"/>
       <c r="AF29" s="16"/>
     </row>
-    <row r="30" customHeight="1" spans="1:32">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="M30" s="15"/>
+      <c r="N30" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="O30" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="R30" s="15"/>
+      <c r="S30" s="16"/>
+      <c r="T30" s="16"/>
+      <c r="U30" s="16"/>
+      <c r="V30" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="W30" s="16"/>
+      <c r="X30" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y30" s="16"/>
+      <c r="Z30" s="15"/>
+      <c r="AA30" s="15"/>
+      <c r="AB30" s="15"/>
+      <c r="AC30" s="15"/>
+      <c r="AD30" s="15"/>
+      <c r="AE30" s="15"/>
+      <c r="AF30" s="15"/>
+    </row>
+    <row r="31" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C31" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D31" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E31" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F31" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G31" s="8">
         <v>2026</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H31" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="I30" s="6" t="str">
-        <f t="shared" si="4"/>
+      <c r="I31" s="6" t="str">
+        <f>IF(B31="英文",H31,"")</f>
         <v>Tourism demand forecasting with multi-source data: a hybrid model incorporating seasonal-trend decomposition</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J31" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K31" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="L30" s="6" t="str">
-        <f>IF(B30="英文",K30,"")</f>
+      <c r="L31" s="6" t="str">
+        <f>IF(B31="英文",K31,"")</f>
         <v>Annals of Operations Research</v>
       </c>
-      <c r="M30" s="6" t="s">
+      <c r="M31" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="N30" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q30" s="6" t="s">
+      <c r="N31" s="20">
+        <v>363</v>
+      </c>
+      <c r="O31" s="8">
+        <v>2</v>
+      </c>
+      <c r="P31" s="20" t="s">
+        <v>658</v>
+      </c>
+      <c r="Q31" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="R30" s="8" t="str" cm="1">
-        <f t="array" ref="R30">_xlfn.LET(_xlpm.issn,TRIM(M30),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.1</v>
-      </c>
-      <c r="S30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6"/>
-      <c r="W30" s="6"/>
-      <c r="X30" s="8" t="s">
+      <c r="R31" s="8" t="str" cm="1">
+        <f t="array" ref="R31">_xlfn.LET(_xlpm.issn,TRIM(M31),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
+        <v/>
+      </c>
+      <c r="S31" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T31" s="8"/>
+      <c r="U31" s="8"/>
+      <c r="V31" s="8"/>
+      <c r="W31" s="8"/>
+      <c r="X31" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="Y30" s="8" t="s">
+      <c r="Y31" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="Z30" s="6"/>
-      <c r="AA30" s="6"/>
-      <c r="AB30" s="6"/>
-      <c r="AC30" s="6"/>
-      <c r="AD30" s="6"/>
-      <c r="AE30" s="6"/>
-      <c r="AF30" s="6"/>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="6"/>
+      <c r="AD31" s="6"/>
+      <c r="AE31" s="6"/>
+      <c r="AF31" s="6"/>
     </row>
-    <row r="31" customHeight="1" spans="1:32">
-      <c r="A31" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="H31" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="I31" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="O31" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="R31" s="15"/>
-      <c r="S31" s="15"/>
-      <c r="T31" s="15"/>
-      <c r="U31" s="15"/>
-      <c r="V31" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="W31" s="15"/>
-      <c r="X31" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="Y31" s="15"/>
-      <c r="Z31" s="15"/>
-      <c r="AA31" s="15"/>
-      <c r="AB31" s="15"/>
-      <c r="AC31" s="15"/>
-      <c r="AD31" s="15"/>
-      <c r="AE31" s="15"/>
-      <c r="AF31" s="15"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:32">
+    <row r="32" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>151</v>
       </c>
@@ -5983,7 +5388,7 @@
       <c r="F32" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="8">
         <v>2026</v>
       </c>
       <c r="H32" s="6" t="s">
@@ -6004,13 +5409,13 @@
       <c r="M32" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="N32" s="6">
+      <c r="N32" s="8">
         <v>334</v>
       </c>
-      <c r="O32" s="6">
+      <c r="O32" s="8">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="s">
+      <c r="P32" s="8" t="s">
         <v>166</v>
       </c>
       <c r="Q32" s="6" t="s">
@@ -6018,17 +5423,17 @@
       </c>
       <c r="R32" s="8" t="str" cm="1">
         <f t="array" ref="R32">_xlfn.LET(_xlpm.issn,TRIM(M32),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.0</v>
-      </c>
-      <c r="S32" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V32" s="6"/>
-      <c r="W32" s="6"/>
+        <v/>
+      </c>
+      <c r="S32" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T32" s="8"/>
+      <c r="U32" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V32" s="8"/>
+      <c r="W32" s="8"/>
       <c r="X32" s="8" t="s">
         <v>45</v>
       </c>
@@ -6043,7 +5448,7 @@
       <c r="AE32" s="6"/>
       <c r="AF32" s="6"/>
     </row>
-    <row r="33" customHeight="1" spans="1:32">
+    <row r="33" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
         <v>151</v>
       </c>
@@ -6062,7 +5467,7 @@
       <c r="F33" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G33" s="16" t="s">
         <v>160</v>
       </c>
       <c r="H33" s="15" t="s">
@@ -6085,13 +5490,13 @@
       <c r="M33" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="N33" s="15" t="s">
+      <c r="N33" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="O33" s="15" t="s">
+      <c r="O33" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P33" s="15" t="s">
+      <c r="P33" s="16" t="s">
         <v>171</v>
       </c>
       <c r="Q33" s="15" t="s">
@@ -6099,17 +5504,17 @@
       </c>
       <c r="R33" s="8" t="str" cm="1">
         <f t="array" ref="R33">_xlfn.LET(_xlpm.issn,TRIM(M33),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>9.4</v>
-      </c>
-      <c r="S33" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T33" s="15"/>
-      <c r="U33" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V33" s="15"/>
-      <c r="W33" s="15"/>
+        <v/>
+      </c>
+      <c r="S33" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T33" s="16"/>
+      <c r="U33" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V33" s="16"/>
+      <c r="W33" s="16"/>
       <c r="X33" s="16"/>
       <c r="Y33" s="16"/>
       <c r="Z33" s="15"/>
@@ -6120,7 +5525,7 @@
       <c r="AE33" s="15"/>
       <c r="AF33" s="15"/>
     </row>
-    <row r="34" customHeight="1" spans="1:32">
+    <row r="34" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>151</v>
       </c>
@@ -6139,7 +5544,7 @@
       <c r="F34" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="8" t="s">
         <v>160</v>
       </c>
       <c r="H34" s="6" t="s">
@@ -6162,13 +5567,13 @@
       <c r="M34" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="N34" s="6" t="s">
+      <c r="N34" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="O34" s="6" t="s">
+      <c r="O34" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P34" s="6" t="s">
+      <c r="P34" s="8" t="s">
         <v>176</v>
       </c>
       <c r="Q34" s="6" t="s">
@@ -6176,17 +5581,17 @@
       </c>
       <c r="R34" s="8" t="str" cm="1">
         <f t="array" ref="R34">_xlfn.LET(_xlpm.issn,TRIM(M34),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>9.4</v>
-      </c>
-      <c r="S34" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
+        <v/>
+      </c>
+      <c r="S34" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T34" s="8"/>
+      <c r="U34" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V34" s="8"/>
+      <c r="W34" s="8"/>
       <c r="X34" s="8" t="s">
         <v>153</v>
       </c>
@@ -6205,7 +5610,7 @@
       <c r="AE34" s="6"/>
       <c r="AF34" s="6"/>
     </row>
-    <row r="35" customHeight="1" spans="1:32">
+    <row r="35" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
         <v>151</v>
       </c>
@@ -6224,7 +5629,7 @@
       <c r="F35" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="G35" s="16" t="s">
         <v>160</v>
       </c>
       <c r="H35" s="15" t="s">
@@ -6245,13 +5650,13 @@
       <c r="M35" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="N35" s="15" t="s">
+      <c r="N35" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="O35" s="15" t="s">
+      <c r="O35" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="P35" s="15" t="s">
+      <c r="P35" s="16" t="s">
         <v>182</v>
       </c>
       <c r="Q35" s="15" t="s">
@@ -6259,17 +5664,17 @@
       </c>
       <c r="R35" s="8" t="str" cm="1">
         <f t="array" ref="R35">_xlfn.LET(_xlpm.issn,TRIM(M35),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>8.4</v>
-      </c>
-      <c r="S35" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T35" s="15"/>
-      <c r="U35" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V35" s="15"/>
-      <c r="W35" s="15"/>
+        <v/>
+      </c>
+      <c r="S35" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T35" s="16"/>
+      <c r="U35" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V35" s="16"/>
+      <c r="W35" s="16"/>
       <c r="X35" s="16" t="s">
         <v>40</v>
       </c>
@@ -6288,7 +5693,7 @@
       <c r="AE35" s="15"/>
       <c r="AF35" s="15"/>
     </row>
-    <row r="36" customHeight="1" spans="1:32">
+    <row r="36" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>151</v>
       </c>
@@ -6307,7 +5712,7 @@
       <c r="F36" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="8" t="s">
         <v>160</v>
       </c>
       <c r="H36" s="6" t="s">
@@ -6328,13 +5733,13 @@
       <c r="M36" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="N36" s="6" t="s">
+      <c r="N36" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="O36" s="6" t="s">
+      <c r="O36" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P36" s="6" t="s">
+      <c r="P36" s="8" t="s">
         <v>188</v>
       </c>
       <c r="Q36" s="6" t="s">
@@ -6342,17 +5747,17 @@
       </c>
       <c r="R36" s="8" t="str" cm="1">
         <f t="array" ref="R36">_xlfn.LET(_xlpm.issn,TRIM(M36),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>17.4</v>
-      </c>
-      <c r="S36" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
+        <v/>
+      </c>
+      <c r="S36" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T36" s="8"/>
+      <c r="U36" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V36" s="8"/>
+      <c r="W36" s="8"/>
       <c r="X36" s="8"/>
       <c r="Y36" s="8"/>
       <c r="Z36" s="6"/>
@@ -6363,7 +5768,7 @@
       <c r="AE36" s="6"/>
       <c r="AF36" s="6"/>
     </row>
-    <row r="37" customHeight="1" spans="1:32">
+    <row r="37" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
         <v>151</v>
       </c>
@@ -6382,7 +5787,7 @@
       <c r="F37" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="G37" s="16" t="s">
         <v>191</v>
       </c>
       <c r="H37" s="15" t="s">
@@ -6403,13 +5808,13 @@
       <c r="M37" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="N37" s="15" t="s">
+      <c r="N37" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="O37" s="15" t="s">
+      <c r="O37" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="P37" s="15" t="s">
+      <c r="P37" s="16" t="s">
         <v>194</v>
       </c>
       <c r="Q37" s="15" t="s">
@@ -6417,17 +5822,17 @@
       </c>
       <c r="R37" s="8" t="str" cm="1">
         <f t="array" ref="R37">_xlfn.LET(_xlpm.issn,TRIM(M37),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.0</v>
-      </c>
-      <c r="S37" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T37" s="15"/>
-      <c r="U37" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
+        <v/>
+      </c>
+      <c r="S37" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T37" s="16"/>
+      <c r="U37" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V37" s="16"/>
+      <c r="W37" s="16"/>
       <c r="X37" s="16" t="s">
         <v>45</v>
       </c>
@@ -6442,7 +5847,7 @@
       <c r="AE37" s="15"/>
       <c r="AF37" s="15"/>
     </row>
-    <row r="38" customHeight="1" spans="1:32">
+    <row r="38" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>151</v>
       </c>
@@ -6461,7 +5866,7 @@
       <c r="F38" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="8" t="s">
         <v>191</v>
       </c>
       <c r="H38" s="6" t="s">
@@ -6482,13 +5887,13 @@
       <c r="M38" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="N38" s="6" t="s">
+      <c r="N38" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="O38" s="6" t="s">
+      <c r="O38" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P38" s="6" t="s">
+      <c r="P38" s="8" t="s">
         <v>198</v>
       </c>
       <c r="Q38" s="6" t="s">
@@ -6496,19 +5901,19 @@
       </c>
       <c r="R38" s="8" t="str" cm="1">
         <f t="array" ref="R38">_xlfn.LET(_xlpm.issn,TRIM(M38),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>6.9</v>
-      </c>
-      <c r="S38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V38" s="6"/>
-      <c r="W38" s="6"/>
+        <v/>
+      </c>
+      <c r="S38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V38" s="8"/>
+      <c r="W38" s="8"/>
       <c r="X38" s="8" t="s">
         <v>40</v>
       </c>
@@ -6527,7 +5932,7 @@
       <c r="AE38" s="6"/>
       <c r="AF38" s="6"/>
     </row>
-    <row r="39" customHeight="1" spans="1:32">
+    <row r="39" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
         <v>151</v>
       </c>
@@ -6546,7 +5951,7 @@
       <c r="F39" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="G39" s="15" t="s">
+      <c r="G39" s="16" t="s">
         <v>191</v>
       </c>
       <c r="H39" s="15" t="s">
@@ -6567,13 +5972,13 @@
       <c r="M39" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="N39" s="15" t="s">
+      <c r="N39" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="O39" s="15" t="s">
+      <c r="O39" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P39" s="15" t="s">
+      <c r="P39" s="16" t="s">
         <v>206</v>
       </c>
       <c r="Q39" s="15" t="s">
@@ -6581,17 +5986,17 @@
       </c>
       <c r="R39" s="8" t="str" cm="1">
         <f t="array" ref="R39">_xlfn.LET(_xlpm.issn,TRIM(M39),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.6</v>
-      </c>
-      <c r="S39" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T39" s="15"/>
-      <c r="U39" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V39" s="15"/>
-      <c r="W39" s="15"/>
+        <v/>
+      </c>
+      <c r="S39" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T39" s="16"/>
+      <c r="U39" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V39" s="16"/>
+      <c r="W39" s="16"/>
       <c r="X39" s="16" t="s">
         <v>40</v>
       </c>
@@ -6606,7 +6011,7 @@
       <c r="AE39" s="15"/>
       <c r="AF39" s="15"/>
     </row>
-    <row r="40" customHeight="1" spans="1:32">
+    <row r="40" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>151</v>
       </c>
@@ -6625,7 +6030,7 @@
       <c r="F40" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="8" t="s">
         <v>191</v>
       </c>
       <c r="H40" s="6" t="s">
@@ -6646,13 +6051,13 @@
       <c r="M40" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="N40" s="6" t="s">
+      <c r="N40" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="O40" s="6" t="s">
+      <c r="O40" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="P40" s="6" t="s">
+      <c r="P40" s="8" t="s">
         <v>212</v>
       </c>
       <c r="Q40" s="6" t="s">
@@ -6660,17 +6065,17 @@
       </c>
       <c r="R40" s="8" t="str" cm="1">
         <f t="array" ref="R40">_xlfn.LET(_xlpm.issn,TRIM(M40),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>8.4</v>
-      </c>
-      <c r="S40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T40" s="6"/>
-      <c r="U40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V40" s="6"/>
-      <c r="W40" s="6"/>
+        <v/>
+      </c>
+      <c r="S40" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T40" s="8"/>
+      <c r="U40" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V40" s="8"/>
+      <c r="W40" s="8"/>
       <c r="X40" s="8" t="s">
         <v>40</v>
       </c>
@@ -6685,7 +6090,7 @@
       <c r="AE40" s="6"/>
       <c r="AF40" s="6"/>
     </row>
-    <row r="41" customHeight="1" spans="1:32">
+    <row r="41" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
         <v>151</v>
       </c>
@@ -6704,7 +6109,7 @@
       <c r="F41" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="G41" s="15" t="s">
+      <c r="G41" s="16" t="s">
         <v>191</v>
       </c>
       <c r="H41" s="15" t="s">
@@ -6725,13 +6130,13 @@
       <c r="M41" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="N41" s="15" t="s">
+      <c r="N41" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="O41" s="15" t="s">
+      <c r="O41" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="P41" s="15" t="s">
+      <c r="P41" s="16" t="s">
         <v>215</v>
       </c>
       <c r="Q41" s="15" t="s">
@@ -6739,17 +6144,17 @@
       </c>
       <c r="R41" s="8" t="str" cm="1">
         <f t="array" ref="R41">_xlfn.LET(_xlpm.issn,TRIM(M41),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>11.3</v>
-      </c>
-      <c r="S41" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T41" s="15"/>
-      <c r="U41" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V41" s="15"/>
-      <c r="W41" s="15"/>
+        <v/>
+      </c>
+      <c r="S41" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T41" s="16"/>
+      <c r="U41" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V41" s="16"/>
+      <c r="W41" s="16"/>
       <c r="X41" s="16" t="s">
         <v>40</v>
       </c>
@@ -6764,7 +6169,7 @@
       <c r="AE41" s="15"/>
       <c r="AF41" s="15"/>
     </row>
-    <row r="42" customHeight="1" spans="1:32">
+    <row r="42" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>151</v>
       </c>
@@ -6783,7 +6188,7 @@
       <c r="F42" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="8" t="s">
         <v>191</v>
       </c>
       <c r="H42" s="6" t="s">
@@ -6804,13 +6209,13 @@
       <c r="M42" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="N42" s="6" t="s">
+      <c r="N42" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="O42" s="6" t="s">
+      <c r="O42" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P42" s="6" t="s">
+      <c r="P42" s="8" t="s">
         <v>220</v>
       </c>
       <c r="Q42" s="6" t="s">
@@ -6818,17 +6223,17 @@
       </c>
       <c r="R42" s="8" t="str" cm="1">
         <f t="array" ref="R42">_xlfn.LET(_xlpm.issn,TRIM(M42),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>6.0</v>
-      </c>
-      <c r="S42" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
+        <v/>
+      </c>
+      <c r="S42" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T42" s="8"/>
+      <c r="U42" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V42" s="8"/>
+      <c r="W42" s="8"/>
       <c r="X42" s="8" t="s">
         <v>40</v>
       </c>
@@ -6841,7 +6246,7 @@
       <c r="AE42" s="6"/>
       <c r="AF42" s="6"/>
     </row>
-    <row r="43" customHeight="1" spans="1:32">
+    <row r="43" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
         <v>151</v>
       </c>
@@ -6860,7 +6265,7 @@
       <c r="F43" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="G43" s="15" t="s">
+      <c r="G43" s="16" t="s">
         <v>191</v>
       </c>
       <c r="H43" s="15" t="s">
@@ -6881,13 +6286,13 @@
       <c r="M43" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="N43" s="15" t="s">
+      <c r="N43" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="O43" s="15" t="s">
+      <c r="O43" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P43" s="15" t="s">
+      <c r="P43" s="16" t="s">
         <v>225</v>
       </c>
       <c r="Q43" s="15" t="s">
@@ -6895,17 +6300,17 @@
       </c>
       <c r="R43" s="8" t="str" cm="1">
         <f t="array" ref="R43">_xlfn.LET(_xlpm.issn,TRIM(M43),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>17.4</v>
-      </c>
-      <c r="S43" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T43" s="15"/>
-      <c r="U43" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V43" s="15"/>
-      <c r="W43" s="15"/>
+        <v/>
+      </c>
+      <c r="S43" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T43" s="16"/>
+      <c r="U43" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V43" s="16"/>
+      <c r="W43" s="16"/>
       <c r="X43" s="16"/>
       <c r="Y43" s="16"/>
       <c r="Z43" s="15"/>
@@ -6916,7 +6321,7 @@
       <c r="AE43" s="15"/>
       <c r="AF43" s="15"/>
     </row>
-    <row r="44" customHeight="1" spans="1:32">
+    <row r="44" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>151</v>
       </c>
@@ -6935,7 +6340,7 @@
       <c r="F44" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="8" t="s">
         <v>191</v>
       </c>
       <c r="H44" s="6" t="s">
@@ -6956,13 +6361,13 @@
       <c r="M44" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="N44" s="6" t="s">
+      <c r="N44" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="O44" s="6" t="s">
+      <c r="O44" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P44" s="6" t="s">
+      <c r="P44" s="8" t="s">
         <v>231</v>
       </c>
       <c r="Q44" s="6" t="s">
@@ -6970,17 +6375,17 @@
       </c>
       <c r="R44" s="8" t="str" cm="1">
         <f t="array" ref="R44">_xlfn.LET(_xlpm.issn,TRIM(M44),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>17.4</v>
-      </c>
-      <c r="S44" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T44" s="6"/>
-      <c r="U44" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V44" s="6"/>
-      <c r="W44" s="6"/>
+        <v/>
+      </c>
+      <c r="S44" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T44" s="8"/>
+      <c r="U44" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V44" s="8"/>
+      <c r="W44" s="8"/>
       <c r="X44" s="8"/>
       <c r="Y44" s="8"/>
       <c r="Z44" s="6" t="s">
@@ -6995,7 +6400,7 @@
       <c r="AE44" s="6"/>
       <c r="AF44" s="6"/>
     </row>
-    <row r="45" customHeight="1" spans="1:32">
+    <row r="45" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
         <v>151</v>
       </c>
@@ -7014,7 +6419,7 @@
       <c r="F45" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="G45" s="15" t="s">
+      <c r="G45" s="16" t="s">
         <v>191</v>
       </c>
       <c r="H45" s="15" t="s">
@@ -7035,13 +6440,13 @@
       <c r="M45" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="N45" s="15" t="s">
+      <c r="N45" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="O45" s="15" t="s">
+      <c r="O45" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="P45" s="15" t="s">
+      <c r="P45" s="16" t="s">
         <v>237</v>
       </c>
       <c r="Q45" s="15" t="s">
@@ -7049,15 +6454,15 @@
       </c>
       <c r="R45" s="8" t="str" cm="1">
         <f t="array" ref="R45">_xlfn.LET(_xlpm.issn,TRIM(M45),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.1</v>
-      </c>
-      <c r="S45" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T45" s="15"/>
-      <c r="U45" s="15"/>
-      <c r="V45" s="15"/>
-      <c r="W45" s="15"/>
+        <v/>
+      </c>
+      <c r="S45" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T45" s="16"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="16"/>
+      <c r="W45" s="16"/>
       <c r="X45" s="16" t="s">
         <v>40</v>
       </c>
@@ -7072,7 +6477,7 @@
       <c r="AE45" s="15"/>
       <c r="AF45" s="15"/>
     </row>
-    <row r="46" customHeight="1" spans="1:32">
+    <row r="46" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>151</v>
       </c>
@@ -7091,7 +6496,7 @@
       <c r="F46" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="8" t="s">
         <v>191</v>
       </c>
       <c r="H46" s="6" t="s">
@@ -7112,13 +6517,13 @@
       <c r="M46" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="N46" s="6" t="s">
+      <c r="N46" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="O46" s="6" t="s">
+      <c r="O46" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="P46" s="6" t="s">
+      <c r="P46" s="8" t="s">
         <v>242</v>
       </c>
       <c r="Q46" s="6" t="s">
@@ -7126,15 +6531,15 @@
       </c>
       <c r="R46" s="8" t="str" cm="1">
         <f t="array" ref="R46">_xlfn.LET(_xlpm.issn,TRIM(M46),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.1</v>
-      </c>
-      <c r="S46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
+        <v/>
+      </c>
+      <c r="S46" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T46" s="8"/>
+      <c r="U46" s="8"/>
+      <c r="V46" s="8"/>
+      <c r="W46" s="8"/>
       <c r="X46" s="8" t="s">
         <v>40</v>
       </c>
@@ -7151,7 +6556,7 @@
       <c r="AE46" s="6"/>
       <c r="AF46" s="6"/>
     </row>
-    <row r="47" customHeight="1" spans="1:32">
+    <row r="47" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="15" t="s">
         <v>151</v>
       </c>
@@ -7170,7 +6575,7 @@
       <c r="F47" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="G47" s="15" t="s">
+      <c r="G47" s="16" t="s">
         <v>191</v>
       </c>
       <c r="H47" s="15" t="s">
@@ -7193,13 +6598,13 @@
       <c r="M47" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="N47" s="15" t="s">
+      <c r="N47" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="O47" s="15" t="s">
+      <c r="O47" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="P47" s="15" t="s">
+      <c r="P47" s="16" t="s">
         <v>249</v>
       </c>
       <c r="Q47" s="15" t="s">
@@ -7207,17 +6612,17 @@
       </c>
       <c r="R47" s="8" t="str" cm="1">
         <f t="array" ref="R47">_xlfn.LET(_xlpm.issn,TRIM(M47),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>3.5</v>
-      </c>
-      <c r="S47" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T47" s="15"/>
-      <c r="U47" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V47" s="15"/>
-      <c r="W47" s="15"/>
+        <v/>
+      </c>
+      <c r="S47" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T47" s="16"/>
+      <c r="U47" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V47" s="16"/>
+      <c r="W47" s="16"/>
       <c r="X47" s="16" t="s">
         <v>153</v>
       </c>
@@ -7236,7 +6641,7 @@
       <c r="AE47" s="15"/>
       <c r="AF47" s="15"/>
     </row>
-    <row r="48" customHeight="1" spans="1:32">
+    <row r="48" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>251</v>
       </c>
@@ -7251,7 +6656,7 @@
       <c r="F48" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="G48" s="8" t="s">
         <v>253</v>
       </c>
       <c r="H48" s="6" t="s">
@@ -7272,13 +6677,13 @@
         <v>Springer Nature</v>
       </c>
       <c r="M48" s="6"/>
-      <c r="N48" s="6" t="s">
+      <c r="N48" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="O48" s="6" t="s">
+      <c r="O48" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P48" s="6" t="s">
+      <c r="P48" s="8" t="s">
         <v>153</v>
       </c>
       <c r="Q48" s="6" t="s">
@@ -7288,13 +6693,13 @@
         <f t="array" ref="R48">_xlfn.LET(_xlpm.issn,TRIM(M48),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S48" s="6"/>
-      <c r="T48" s="6"/>
-      <c r="U48" s="6"/>
-      <c r="V48" s="6"/>
-      <c r="W48" s="6"/>
-      <c r="X48" s="6"/>
-      <c r="Y48" s="6"/>
+      <c r="S48" s="8"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="8"/>
+      <c r="V48" s="8"/>
+      <c r="W48" s="8"/>
+      <c r="X48" s="8"/>
+      <c r="Y48" s="8"/>
       <c r="Z48" s="6"/>
       <c r="AA48" s="6"/>
       <c r="AB48" s="6"/>
@@ -7305,7 +6710,7 @@
       <c r="AE48" s="6"/>
       <c r="AF48" s="6"/>
     </row>
-    <row r="49" customHeight="1" spans="1:32">
+    <row r="49" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
         <v>151</v>
       </c>
@@ -7324,7 +6729,7 @@
       <c r="F49" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="G49" s="15" t="s">
+      <c r="G49" s="16" t="s">
         <v>253</v>
       </c>
       <c r="H49" s="15" t="s">
@@ -7345,13 +6750,13 @@
       <c r="M49" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="N49" s="15" t="s">
+      <c r="N49" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="O49" s="15" t="s">
+      <c r="O49" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P49" s="15" t="s">
+      <c r="P49" s="16" t="s">
         <v>264</v>
       </c>
       <c r="Q49" s="15" t="s">
@@ -7359,17 +6764,17 @@
       </c>
       <c r="R49" s="8" t="str" cm="1">
         <f t="array" ref="R49">_xlfn.LET(_xlpm.issn,TRIM(M49),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>9.0</v>
-      </c>
-      <c r="S49" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T49" s="15"/>
-      <c r="U49" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V49" s="15"/>
-      <c r="W49" s="15"/>
+        <v/>
+      </c>
+      <c r="S49" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T49" s="16"/>
+      <c r="U49" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V49" s="16"/>
+      <c r="W49" s="16"/>
       <c r="X49" s="16"/>
       <c r="Y49" s="16"/>
       <c r="Z49" s="15"/>
@@ -7380,7 +6785,7 @@
       <c r="AE49" s="15"/>
       <c r="AF49" s="15"/>
     </row>
-    <row r="50" customHeight="1" spans="1:32">
+    <row r="50" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>151</v>
       </c>
@@ -7399,7 +6804,7 @@
       <c r="F50" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="8" t="s">
         <v>253</v>
       </c>
       <c r="H50" s="6" t="s">
@@ -7420,13 +6825,13 @@
       <c r="M50" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="N50" s="6" t="s">
+      <c r="N50" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="O50" s="6" t="s">
+      <c r="O50" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="P50" s="6" t="s">
+      <c r="P50" s="8" t="s">
         <v>273</v>
       </c>
       <c r="Q50" s="6" t="s">
@@ -7434,17 +6839,17 @@
       </c>
       <c r="R50" s="8" t="str" cm="1">
         <f t="array" ref="R50">_xlfn.LET(_xlpm.issn,TRIM(M50),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>10.2</v>
-      </c>
-      <c r="S50" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
+        <v/>
+      </c>
+      <c r="S50" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T50" s="8"/>
+      <c r="U50" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V50" s="8"/>
+      <c r="W50" s="8"/>
       <c r="X50" s="8"/>
       <c r="Y50" s="8"/>
       <c r="Z50" s="6"/>
@@ -7455,7 +6860,7 @@
       <c r="AE50" s="6"/>
       <c r="AF50" s="6"/>
     </row>
-    <row r="51" customHeight="1" spans="1:32">
+    <row r="51" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="15" t="s">
         <v>151</v>
       </c>
@@ -7474,7 +6879,7 @@
       <c r="F51" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="G51" s="15" t="s">
+      <c r="G51" s="16" t="s">
         <v>253</v>
       </c>
       <c r="H51" s="15" t="s">
@@ -7495,13 +6900,13 @@
       <c r="M51" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="N51" s="15" t="s">
+      <c r="N51" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="O51" s="15" t="s">
+      <c r="O51" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="P51" s="15" t="s">
+      <c r="P51" s="16" t="s">
         <v>277</v>
       </c>
       <c r="Q51" s="15" t="s">
@@ -7509,19 +6914,19 @@
       </c>
       <c r="R51" s="8" t="str" cm="1">
         <f t="array" ref="R51">_xlfn.LET(_xlpm.issn,TRIM(M51),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>2.6</v>
-      </c>
-      <c r="S51" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T51" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="U51" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
+        <v/>
+      </c>
+      <c r="S51" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T51" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="U51" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V51" s="16"/>
+      <c r="W51" s="16"/>
       <c r="X51" s="16" t="s">
         <v>40</v>
       </c>
@@ -7538,7 +6943,7 @@
       <c r="AE51" s="15"/>
       <c r="AF51" s="15"/>
     </row>
-    <row r="52" customHeight="1" spans="1:32">
+    <row r="52" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>151</v>
       </c>
@@ -7557,7 +6962,7 @@
       <c r="F52" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" s="8" t="s">
         <v>253</v>
       </c>
       <c r="H52" s="6" t="s">
@@ -7578,13 +6983,13 @@
       <c r="M52" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="N52" s="6" t="s">
+      <c r="N52" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="O52" s="6" t="s">
+      <c r="O52" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="P52" s="6" t="s">
+      <c r="P52" s="8" t="s">
         <v>283</v>
       </c>
       <c r="Q52" s="6" t="s">
@@ -7592,17 +6997,17 @@
       </c>
       <c r="R52" s="8" t="str" cm="1">
         <f t="array" ref="R52">_xlfn.LET(_xlpm.issn,TRIM(M52),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.6</v>
-      </c>
-      <c r="S52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V52" s="6"/>
-      <c r="W52" s="6"/>
+        <v/>
+      </c>
+      <c r="S52" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T52" s="8"/>
+      <c r="U52" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V52" s="8"/>
+      <c r="W52" s="8"/>
       <c r="X52" s="8"/>
       <c r="Y52" s="8"/>
       <c r="Z52" s="6" t="s">
@@ -7615,7 +7020,7 @@
       <c r="AE52" s="6"/>
       <c r="AF52" s="6"/>
     </row>
-    <row r="53" customHeight="1" spans="1:32">
+    <row r="53" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
         <v>151</v>
       </c>
@@ -7634,7 +7039,7 @@
       <c r="F53" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="G53" s="15" t="s">
+      <c r="G53" s="16" t="s">
         <v>286</v>
       </c>
       <c r="H53" s="15" t="s">
@@ -7655,13 +7060,13 @@
       <c r="M53" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="N53" s="15" t="s">
+      <c r="N53" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="O53" s="15" t="s">
+      <c r="O53" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P53" s="15" t="s">
+      <c r="P53" s="16" t="s">
         <v>289</v>
       </c>
       <c r="Q53" s="15" t="s">
@@ -7669,17 +7074,17 @@
       </c>
       <c r="R53" s="8" t="str" cm="1">
         <f t="array" ref="R53">_xlfn.LET(_xlpm.issn,TRIM(M53),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>17.4</v>
-      </c>
-      <c r="S53" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T53" s="15"/>
-      <c r="U53" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V53" s="15"/>
-      <c r="W53" s="15"/>
+        <v/>
+      </c>
+      <c r="S53" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T53" s="16"/>
+      <c r="U53" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V53" s="16"/>
+      <c r="W53" s="16"/>
       <c r="X53" s="16"/>
       <c r="Y53" s="16"/>
       <c r="Z53" s="15" t="s">
@@ -7692,7 +7097,7 @@
       <c r="AE53" s="15"/>
       <c r="AF53" s="15"/>
     </row>
-    <row r="54" customHeight="1" spans="1:32">
+    <row r="54" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>151</v>
       </c>
@@ -7711,7 +7116,7 @@
       <c r="F54" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="G54" s="8" t="s">
         <v>286</v>
       </c>
       <c r="H54" s="6" t="s">
@@ -7732,13 +7137,13 @@
       <c r="M54" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="N54" s="6" t="s">
+      <c r="N54" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="O54" s="6" t="s">
+      <c r="O54" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="P54" s="6" t="s">
+      <c r="P54" s="8" t="s">
         <v>296</v>
       </c>
       <c r="Q54" s="6" t="s">
@@ -7746,17 +7151,17 @@
       </c>
       <c r="R54" s="8" t="str" cm="1">
         <f t="array" ref="R54">_xlfn.LET(_xlpm.issn,TRIM(M54),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>3.5</v>
-      </c>
-      <c r="S54" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V54" s="6"/>
-      <c r="W54" s="6"/>
+        <v/>
+      </c>
+      <c r="S54" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T54" s="8"/>
+      <c r="U54" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V54" s="8"/>
+      <c r="W54" s="8"/>
       <c r="X54" s="8"/>
       <c r="Y54" s="8"/>
       <c r="Z54" s="6"/>
@@ -7767,7 +7172,7 @@
       <c r="AE54" s="6"/>
       <c r="AF54" s="6"/>
     </row>
-    <row r="55" customHeight="1" spans="1:32">
+    <row r="55" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
         <v>151</v>
       </c>
@@ -7786,7 +7191,7 @@
       <c r="F55" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="G55" s="15" t="s">
+      <c r="G55" s="16" t="s">
         <v>286</v>
       </c>
       <c r="H55" s="15" t="s">
@@ -7807,13 +7212,13 @@
       <c r="M55" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="N55" s="15" t="s">
+      <c r="N55" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="O55" s="15" t="s">
+      <c r="O55" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="P55" s="15" t="s">
+      <c r="P55" s="16" t="s">
         <v>302</v>
       </c>
       <c r="Q55" s="15" t="s">
@@ -7821,15 +7226,15 @@
       </c>
       <c r="R55" s="8" t="str" cm="1">
         <f t="array" ref="R55">_xlfn.LET(_xlpm.issn,TRIM(M55),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>3.8</v>
-      </c>
-      <c r="S55" s="15"/>
-      <c r="T55" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="U55" s="15"/>
-      <c r="V55" s="15"/>
-      <c r="W55" s="15"/>
+        <v/>
+      </c>
+      <c r="S55" s="16"/>
+      <c r="T55" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="U55" s="16"/>
+      <c r="V55" s="16"/>
+      <c r="W55" s="16"/>
       <c r="X55" s="16"/>
       <c r="Y55" s="16"/>
       <c r="Z55" s="15" t="s">
@@ -7844,7 +7249,7 @@
       <c r="AE55" s="15"/>
       <c r="AF55" s="15"/>
     </row>
-    <row r="56" customHeight="1" spans="1:32">
+    <row r="56" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>151</v>
       </c>
@@ -7863,7 +7268,7 @@
       <c r="F56" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="G56" s="8" t="s">
         <v>286</v>
       </c>
       <c r="H56" s="6" t="s">
@@ -7884,13 +7289,13 @@
       <c r="M56" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="N56" s="6" t="s">
+      <c r="N56" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="O56" s="6" t="s">
+      <c r="O56" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="P56" s="6" t="s">
+      <c r="P56" s="8" t="s">
         <v>307</v>
       </c>
       <c r="Q56" s="6" t="s">
@@ -7898,15 +7303,15 @@
       </c>
       <c r="R56" s="8" t="str" cm="1">
         <f t="array" ref="R56">_xlfn.LET(_xlpm.issn,TRIM(M56),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.1</v>
-      </c>
-      <c r="S56" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T56" s="6"/>
-      <c r="U56" s="6"/>
-      <c r="V56" s="6"/>
-      <c r="W56" s="6"/>
+        <v/>
+      </c>
+      <c r="S56" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T56" s="8"/>
+      <c r="U56" s="8"/>
+      <c r="V56" s="8"/>
+      <c r="W56" s="8"/>
       <c r="X56" s="8" t="s">
         <v>40</v>
       </c>
@@ -7923,7 +7328,7 @@
       <c r="AE56" s="6"/>
       <c r="AF56" s="6"/>
     </row>
-    <row r="57" customHeight="1" spans="1:32">
+    <row r="57" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="15" t="s">
         <v>151</v>
       </c>
@@ -7942,7 +7347,7 @@
       <c r="F57" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="G57" s="15" t="s">
+      <c r="G57" s="16" t="s">
         <v>286</v>
       </c>
       <c r="H57" s="15" t="s">
@@ -7963,13 +7368,13 @@
       <c r="M57" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="N57" s="15" t="s">
+      <c r="N57" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="O57" s="15" t="s">
+      <c r="O57" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="P57" s="15" t="s">
+      <c r="P57" s="16" t="s">
         <v>311</v>
       </c>
       <c r="Q57" s="15" t="s">
@@ -7977,15 +7382,15 @@
       </c>
       <c r="R57" s="8" t="str" cm="1">
         <f t="array" ref="R57">_xlfn.LET(_xlpm.issn,TRIM(M57),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>2.8</v>
-      </c>
-      <c r="S57" s="15"/>
-      <c r="T57" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="U57" s="15"/>
-      <c r="V57" s="15"/>
-      <c r="W57" s="15"/>
+        <v/>
+      </c>
+      <c r="S57" s="16"/>
+      <c r="T57" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="U57" s="16"/>
+      <c r="V57" s="16"/>
+      <c r="W57" s="16"/>
       <c r="X57" s="16" t="s">
         <v>40</v>
       </c>
@@ -8004,7 +7409,7 @@
       <c r="AE57" s="15"/>
       <c r="AF57" s="15"/>
     </row>
-    <row r="58" customHeight="1" spans="1:32">
+    <row r="58" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>151</v>
       </c>
@@ -8023,7 +7428,7 @@
       <c r="F58" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="G58" s="6" t="s">
+      <c r="G58" s="8" t="s">
         <v>286</v>
       </c>
       <c r="H58" s="6" t="s">
@@ -8040,30 +7445,30 @@
         <v>317</v>
       </c>
       <c r="M58" s="6"/>
-      <c r="N58" s="6" t="s">
+      <c r="N58" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="O58" s="6" t="s">
+      <c r="O58" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="P58" s="6" t="s">
+      <c r="P58" s="8" t="s">
         <v>319</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>320</v>
       </c>
       <c r="R58" s="6"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="W58" s="6"/>
-      <c r="X58" s="6" t="s">
+      <c r="S58" s="8"/>
+      <c r="T58" s="8"/>
+      <c r="U58" s="8"/>
+      <c r="V58" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="W58" s="8"/>
+      <c r="X58" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="Y58" s="6"/>
+      <c r="Y58" s="8"/>
       <c r="Z58" s="6"/>
       <c r="AA58" s="6"/>
       <c r="AB58" s="6"/>
@@ -8072,7 +7477,7 @@
       <c r="AE58" s="6"/>
       <c r="AF58" s="6"/>
     </row>
-    <row r="59" customHeight="1" spans="1:32">
+    <row r="59" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="15" t="s">
         <v>151</v>
       </c>
@@ -8091,7 +7496,7 @@
       <c r="F59" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="G59" s="15" t="s">
+      <c r="G59" s="16" t="s">
         <v>323</v>
       </c>
       <c r="H59" s="15" t="s">
@@ -8112,13 +7517,13 @@
       <c r="M59" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="N59" s="15" t="s">
+      <c r="N59" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="O59" s="15" t="s">
+      <c r="O59" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="P59" s="15" t="s">
+      <c r="P59" s="16" t="s">
         <v>276</v>
       </c>
       <c r="Q59" s="15" t="s">
@@ -8126,17 +7531,17 @@
       </c>
       <c r="R59" s="8" t="str" cm="1">
         <f t="array" ref="R59">_xlfn.LET(_xlpm.issn,TRIM(M59),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.0</v>
-      </c>
-      <c r="S59" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T59" s="15"/>
-      <c r="U59" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V59" s="15"/>
-      <c r="W59" s="15"/>
+        <v/>
+      </c>
+      <c r="S59" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T59" s="16"/>
+      <c r="U59" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V59" s="16"/>
+      <c r="W59" s="16"/>
       <c r="X59" s="16"/>
       <c r="Y59" s="16"/>
       <c r="Z59" s="15"/>
@@ -8147,7 +7552,7 @@
       <c r="AE59" s="15"/>
       <c r="AF59" s="15"/>
     </row>
-    <row r="60" customHeight="1" spans="1:32">
+    <row r="60" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>151</v>
       </c>
@@ -8166,7 +7571,7 @@
       <c r="F60" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="G60" s="6" t="s">
+      <c r="G60" s="8" t="s">
         <v>323</v>
       </c>
       <c r="H60" s="6" t="s">
@@ -8187,13 +7592,13 @@
       <c r="M60" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="N60" s="6" t="s">
+      <c r="N60" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="O60" s="6" t="s">
+      <c r="O60" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P60" s="6" t="s">
+      <c r="P60" s="8" t="s">
         <v>333</v>
       </c>
       <c r="Q60" s="6" t="s">
@@ -8201,15 +7606,15 @@
       </c>
       <c r="R60" s="8" t="str" cm="1">
         <f t="array" ref="R60">_xlfn.LET(_xlpm.issn,TRIM(M60),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.6</v>
-      </c>
-      <c r="S60" s="6"/>
-      <c r="T60" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U60" s="6"/>
-      <c r="V60" s="6"/>
-      <c r="W60" s="6"/>
+        <v/>
+      </c>
+      <c r="S60" s="8"/>
+      <c r="T60" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U60" s="8"/>
+      <c r="V60" s="8"/>
+      <c r="W60" s="8"/>
       <c r="X60" s="8"/>
       <c r="Y60" s="8" t="s">
         <v>181</v>
@@ -8222,7 +7627,7 @@
       <c r="AE60" s="6"/>
       <c r="AF60" s="6"/>
     </row>
-    <row r="61" customHeight="1" spans="1:32">
+    <row r="61" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="15" t="s">
         <v>151</v>
       </c>
@@ -8241,7 +7646,7 @@
       <c r="F61" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="G61" s="15" t="s">
+      <c r="G61" s="16" t="s">
         <v>323</v>
       </c>
       <c r="H61" s="15" t="s">
@@ -8262,13 +7667,13 @@
       <c r="M61" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="N61" s="15" t="s">
+      <c r="N61" s="16" t="s">
         <v>340</v>
       </c>
-      <c r="O61" s="15" t="s">
+      <c r="O61" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="P61" s="15" t="s">
+      <c r="P61" s="16" t="s">
         <v>341</v>
       </c>
       <c r="Q61" s="15" t="s">
@@ -8276,17 +7681,17 @@
       </c>
       <c r="R61" s="8" t="str" cm="1">
         <f t="array" ref="R61">_xlfn.LET(_xlpm.issn,TRIM(M61),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>2.6</v>
-      </c>
-      <c r="S61" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T61" s="15"/>
-      <c r="U61" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V61" s="15"/>
-      <c r="W61" s="15"/>
+        <v/>
+      </c>
+      <c r="S61" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T61" s="16"/>
+      <c r="U61" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V61" s="16"/>
+      <c r="W61" s="16"/>
       <c r="X61" s="16"/>
       <c r="Y61" s="16"/>
       <c r="Z61" s="15"/>
@@ -8297,7 +7702,7 @@
       <c r="AE61" s="15"/>
       <c r="AF61" s="15"/>
     </row>
-    <row r="62" customHeight="1" spans="1:32">
+    <row r="62" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>151</v>
       </c>
@@ -8316,7 +7721,7 @@
       <c r="F62" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G62" s="6" t="s">
+      <c r="G62" s="8" t="s">
         <v>323</v>
       </c>
       <c r="H62" s="6" t="s">
@@ -8337,13 +7742,13 @@
       <c r="M62" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="N62" s="6" t="s">
+      <c r="N62" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="O62" s="6" t="s">
+      <c r="O62" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P62" s="6" t="s">
+      <c r="P62" s="8" t="s">
         <v>345</v>
       </c>
       <c r="Q62" s="6" t="s">
@@ -8351,17 +7756,17 @@
       </c>
       <c r="R62" s="8" t="str" cm="1">
         <f t="array" ref="R62">_xlfn.LET(_xlpm.issn,TRIM(M62),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.3</v>
-      </c>
-      <c r="S62" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
+        <v/>
+      </c>
+      <c r="S62" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T62" s="8"/>
+      <c r="U62" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V62" s="8"/>
+      <c r="W62" s="8"/>
       <c r="X62" s="8" t="s">
         <v>40</v>
       </c>
@@ -8378,7 +7783,7 @@
       <c r="AE62" s="6"/>
       <c r="AF62" s="6"/>
     </row>
-    <row r="63" customHeight="1" spans="1:32">
+    <row r="63" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="15" t="s">
         <v>151</v>
       </c>
@@ -8397,7 +7802,7 @@
       <c r="F63" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="G63" s="15" t="s">
+      <c r="G63" s="16" t="s">
         <v>323</v>
       </c>
       <c r="H63" s="15" t="s">
@@ -8418,13 +7823,13 @@
       <c r="M63" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="N63" s="15" t="s">
+      <c r="N63" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="O63" s="15" t="s">
+      <c r="O63" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P63" s="15" t="s">
+      <c r="P63" s="16" t="s">
         <v>350</v>
       </c>
       <c r="Q63" s="15" t="s">
@@ -8432,17 +7837,17 @@
       </c>
       <c r="R63" s="8" t="str" cm="1">
         <f t="array" ref="R63">_xlfn.LET(_xlpm.issn,TRIM(M63),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>9.4</v>
-      </c>
-      <c r="S63" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T63" s="15"/>
-      <c r="U63" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V63" s="15"/>
-      <c r="W63" s="15"/>
+        <v/>
+      </c>
+      <c r="S63" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T63" s="16"/>
+      <c r="U63" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V63" s="16"/>
+      <c r="W63" s="16"/>
       <c r="X63" s="16"/>
       <c r="Y63" s="16"/>
       <c r="Z63" s="15"/>
@@ -8453,7 +7858,7 @@
       <c r="AE63" s="15"/>
       <c r="AF63" s="15"/>
     </row>
-    <row r="64" customHeight="1" spans="1:32">
+    <row r="64" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>151</v>
       </c>
@@ -8472,7 +7877,7 @@
       <c r="F64" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="G64" s="6" t="s">
+      <c r="G64" s="8" t="s">
         <v>323</v>
       </c>
       <c r="H64" s="6" t="s">
@@ -8493,13 +7898,13 @@
       <c r="M64" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="N64" s="6" t="s">
+      <c r="N64" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="O64" s="6" t="s">
+      <c r="O64" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="P64" s="6" t="s">
+      <c r="P64" s="8" t="s">
         <v>355</v>
       </c>
       <c r="Q64" s="6" t="s">
@@ -8507,17 +7912,17 @@
       </c>
       <c r="R64" s="8" t="str" cm="1">
         <f t="array" ref="R64">_xlfn.LET(_xlpm.issn,TRIM(M64),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>8.4</v>
-      </c>
-      <c r="S64" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V64" s="6"/>
-      <c r="W64" s="6"/>
+        <v/>
+      </c>
+      <c r="S64" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T64" s="8"/>
+      <c r="U64" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V64" s="8"/>
+      <c r="W64" s="8"/>
       <c r="X64" s="8" t="s">
         <v>40</v>
       </c>
@@ -8536,7 +7941,7 @@
       <c r="AE64" s="6"/>
       <c r="AF64" s="6"/>
     </row>
-    <row r="65" customHeight="1" spans="1:32">
+    <row r="65" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="15" t="s">
         <v>151</v>
       </c>
@@ -8555,7 +7960,7 @@
       <c r="F65" s="15" t="s">
         <v>357</v>
       </c>
-      <c r="G65" s="15" t="s">
+      <c r="G65" s="16" t="s">
         <v>323</v>
       </c>
       <c r="H65" s="15" t="s">
@@ -8576,13 +7981,13 @@
       <c r="M65" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="N65" s="15" t="s">
+      <c r="N65" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="O65" s="15" t="s">
+      <c r="O65" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="P65" s="15" t="s">
+      <c r="P65" s="16" t="s">
         <v>360</v>
       </c>
       <c r="Q65" s="15" t="s">
@@ -8590,19 +7995,19 @@
       </c>
       <c r="R65" s="8" t="str" cm="1">
         <f t="array" ref="R65">_xlfn.LET(_xlpm.issn,TRIM(M65),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>2.6</v>
-      </c>
-      <c r="S65" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T65" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="U65" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V65" s="15"/>
-      <c r="W65" s="15"/>
+        <v/>
+      </c>
+      <c r="S65" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T65" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="U65" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V65" s="16"/>
+      <c r="W65" s="16"/>
       <c r="X65" s="16" t="s">
         <v>40</v>
       </c>
@@ -8621,7 +8026,7 @@
       <c r="AE65" s="15"/>
       <c r="AF65" s="15"/>
     </row>
-    <row r="66" customHeight="1" spans="1:32">
+    <row r="66" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>151</v>
       </c>
@@ -8640,7 +8045,7 @@
       <c r="F66" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="G66" s="6" t="s">
+      <c r="G66" s="8" t="s">
         <v>323</v>
       </c>
       <c r="H66" s="6" t="s">
@@ -8661,13 +8066,13 @@
       <c r="M66" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="N66" s="6" t="s">
+      <c r="N66" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="O66" s="6" t="s">
+      <c r="O66" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P66" s="6" t="s">
+      <c r="P66" s="8" t="s">
         <v>366</v>
       </c>
       <c r="Q66" s="6" t="s">
@@ -8675,19 +8080,19 @@
       </c>
       <c r="R66" s="8" t="str" cm="1">
         <f t="array" ref="R66">_xlfn.LET(_xlpm.issn,TRIM(M66),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>17.4</v>
-      </c>
-      <c r="S66" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T66" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U66" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V66" s="6"/>
-      <c r="W66" s="6"/>
+        <v/>
+      </c>
+      <c r="S66" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T66" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U66" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V66" s="8"/>
+      <c r="W66" s="8"/>
       <c r="X66" s="8"/>
       <c r="Y66" s="8"/>
       <c r="Z66" s="6"/>
@@ -8698,7 +8103,7 @@
       <c r="AE66" s="6"/>
       <c r="AF66" s="6"/>
     </row>
-    <row r="67" customHeight="1" spans="1:32">
+    <row r="67" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="15" t="s">
         <v>151</v>
       </c>
@@ -8717,7 +8122,7 @@
       <c r="F67" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="G67" s="15" t="s">
+      <c r="G67" s="16" t="s">
         <v>369</v>
       </c>
       <c r="H67" s="15" t="s">
@@ -8738,13 +8143,13 @@
       <c r="M67" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="N67" s="15" t="s">
+      <c r="N67" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="O67" s="15" t="s">
+      <c r="O67" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P67" s="15" t="s">
+      <c r="P67" s="16" t="s">
         <v>372</v>
       </c>
       <c r="Q67" s="15" t="s">
@@ -8752,17 +8157,17 @@
       </c>
       <c r="R67" s="8" t="str" cm="1">
         <f t="array" ref="R67">_xlfn.LET(_xlpm.issn,TRIM(M67),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>17.4</v>
-      </c>
-      <c r="S67" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T67" s="15"/>
-      <c r="U67" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V67" s="15"/>
-      <c r="W67" s="15"/>
+        <v/>
+      </c>
+      <c r="S67" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T67" s="16"/>
+      <c r="U67" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V67" s="16"/>
+      <c r="W67" s="16"/>
       <c r="X67" s="16"/>
       <c r="Y67" s="16"/>
       <c r="Z67" s="15" t="s">
@@ -8775,7 +8180,7 @@
       <c r="AE67" s="15"/>
       <c r="AF67" s="15"/>
     </row>
-    <row r="68" customHeight="1" spans="1:32">
+    <row r="68" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>151</v>
       </c>
@@ -8794,7 +8199,7 @@
       <c r="F68" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="G68" s="8" t="s">
         <v>369</v>
       </c>
       <c r="H68" s="6" t="s">
@@ -8811,26 +8216,26 @@
         <v>381</v>
       </c>
       <c r="M68" s="6"/>
-      <c r="N68" s="6" t="s">
+      <c r="N68" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="O68" s="6" t="s">
+      <c r="O68" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="P68" s="6" t="s">
+      <c r="P68" s="8" t="s">
         <v>383</v>
       </c>
       <c r="Q68" s="6" t="s">
         <v>384</v>
       </c>
       <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
-      <c r="V68" s="6"/>
-      <c r="W68" s="6"/>
-      <c r="X68" s="6"/>
-      <c r="Y68" s="6"/>
+      <c r="S68" s="8"/>
+      <c r="T68" s="8"/>
+      <c r="U68" s="8"/>
+      <c r="V68" s="8"/>
+      <c r="W68" s="8"/>
+      <c r="X68" s="8"/>
+      <c r="Y68" s="8"/>
       <c r="Z68" s="6"/>
       <c r="AA68" s="6"/>
       <c r="AB68" s="6"/>
@@ -8839,7 +8244,7 @@
       <c r="AE68" s="6"/>
       <c r="AF68" s="6"/>
     </row>
-    <row r="69" customHeight="1" spans="1:32">
+    <row r="69" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="15" t="s">
         <v>151</v>
       </c>
@@ -8858,7 +8263,7 @@
       <c r="F69" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="G69" s="15" t="s">
+      <c r="G69" s="16" t="s">
         <v>369</v>
       </c>
       <c r="H69" s="15" t="s">
@@ -8879,13 +8284,13 @@
       <c r="M69" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="N69" s="15" t="s">
+      <c r="N69" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="O69" s="15" t="s">
+      <c r="O69" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="P69" s="15" t="s">
+      <c r="P69" s="16" t="s">
         <v>390</v>
       </c>
       <c r="Q69" s="15" t="s">
@@ -8893,17 +8298,17 @@
       </c>
       <c r="R69" s="8" t="str" cm="1">
         <f t="array" ref="R69">_xlfn.LET(_xlpm.issn,TRIM(M69),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>2.1</v>
-      </c>
-      <c r="S69" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T69" s="15"/>
-      <c r="U69" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V69" s="15"/>
-      <c r="W69" s="15"/>
+        <v/>
+      </c>
+      <c r="S69" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T69" s="16"/>
+      <c r="U69" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V69" s="16"/>
+      <c r="W69" s="16"/>
       <c r="X69" s="16"/>
       <c r="Y69" s="16"/>
       <c r="Z69" s="15"/>
@@ -8914,7 +8319,7 @@
       <c r="AE69" s="15"/>
       <c r="AF69" s="15"/>
     </row>
-    <row r="70" customHeight="1" spans="1:32">
+    <row r="70" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>151</v>
       </c>
@@ -8933,7 +8338,7 @@
       <c r="F70" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="G70" s="6" t="s">
+      <c r="G70" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H70" s="6" t="s">
@@ -8954,13 +8359,13 @@
       <c r="M70" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="N70" s="6" t="s">
+      <c r="N70" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="O70" s="6" t="s">
+      <c r="O70" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P70" s="6" t="s">
+      <c r="P70" s="8" t="s">
         <v>397</v>
       </c>
       <c r="Q70" s="6" t="s">
@@ -8968,19 +8373,19 @@
       </c>
       <c r="R70" s="8" t="str" cm="1">
         <f t="array" ref="R70">_xlfn.LET(_xlpm.issn,TRIM(M70),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>1.6</v>
-      </c>
-      <c r="S70" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T70" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U70" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V70" s="6"/>
-      <c r="W70" s="6"/>
+        <v/>
+      </c>
+      <c r="S70" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T70" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U70" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V70" s="8"/>
+      <c r="W70" s="8"/>
       <c r="X70" s="8"/>
       <c r="Y70" s="8"/>
       <c r="Z70" s="6"/>
@@ -8991,7 +8396,7 @@
       <c r="AE70" s="6"/>
       <c r="AF70" s="6"/>
     </row>
-    <row r="71" customHeight="1" spans="1:32">
+    <row r="71" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="15" t="s">
         <v>151</v>
       </c>
@@ -9010,7 +8415,7 @@
       <c r="F71" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="G71" s="15" t="s">
+      <c r="G71" s="16" t="s">
         <v>369</v>
       </c>
       <c r="H71" s="15" t="s">
@@ -9031,13 +8436,13 @@
       <c r="M71" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="N71" s="15" t="s">
+      <c r="N71" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="O71" s="15" t="s">
+      <c r="O71" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P71" s="15" t="s">
+      <c r="P71" s="16" t="s">
         <v>402</v>
       </c>
       <c r="Q71" s="15" t="s">
@@ -9045,19 +8450,19 @@
       </c>
       <c r="R71" s="8" t="str" cm="1">
         <f t="array" ref="R71">_xlfn.LET(_xlpm.issn,TRIM(M71),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>9.4</v>
-      </c>
-      <c r="S71" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T71" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="U71" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V71" s="15"/>
-      <c r="W71" s="15"/>
+        <v/>
+      </c>
+      <c r="S71" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T71" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="U71" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V71" s="16"/>
+      <c r="W71" s="16"/>
       <c r="X71" s="16"/>
       <c r="Y71" s="16"/>
       <c r="Z71" s="15" t="s">
@@ -9070,7 +8475,7 @@
       <c r="AE71" s="15"/>
       <c r="AF71" s="15"/>
     </row>
-    <row r="72" customHeight="1" spans="1:32">
+    <row r="72" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>151</v>
       </c>
@@ -9089,7 +8494,7 @@
       <c r="F72" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="G72" s="6" t="s">
+      <c r="G72" s="8" t="s">
         <v>369</v>
       </c>
       <c r="H72" s="6" t="s">
@@ -9110,13 +8515,13 @@
       <c r="M72" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="N72" s="6" t="s">
+      <c r="N72" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="O72" s="6" t="s">
+      <c r="O72" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P72" s="6" t="s">
+      <c r="P72" s="8" t="s">
         <v>408</v>
       </c>
       <c r="Q72" s="6" t="s">
@@ -9124,19 +8529,19 @@
       </c>
       <c r="R72" s="8" t="str" cm="1">
         <f t="array" ref="R72">_xlfn.LET(_xlpm.issn,TRIM(M72),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>17.4</v>
-      </c>
-      <c r="S72" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T72" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U72" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V72" s="6"/>
-      <c r="W72" s="6"/>
+        <v/>
+      </c>
+      <c r="S72" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T72" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U72" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V72" s="8"/>
+      <c r="W72" s="8"/>
       <c r="X72" s="8"/>
       <c r="Y72" s="8"/>
       <c r="Z72" s="6" t="s">
@@ -9149,7 +8554,7 @@
       <c r="AE72" s="6"/>
       <c r="AF72" s="6"/>
     </row>
-    <row r="73" customHeight="1" spans="1:32">
+    <row r="73" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="15" t="s">
         <v>151</v>
       </c>
@@ -9168,7 +8573,7 @@
       <c r="F73" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="G73" s="15" t="s">
+      <c r="G73" s="16" t="s">
         <v>369</v>
       </c>
       <c r="H73" s="15" t="s">
@@ -9189,13 +8594,13 @@
       <c r="M73" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="N73" s="15" t="s">
+      <c r="N73" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="O73" s="15" t="s">
+      <c r="O73" s="16" t="s">
         <v>413</v>
       </c>
-      <c r="P73" s="15" t="s">
+      <c r="P73" s="16" t="s">
         <v>414</v>
       </c>
       <c r="Q73" s="15" t="s">
@@ -9203,19 +8608,19 @@
       </c>
       <c r="R73" s="8" t="str" cm="1">
         <f t="array" ref="R73">_xlfn.LET(_xlpm.issn,TRIM(M73),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>2.6</v>
-      </c>
-      <c r="S73" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T73" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="U73" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V73" s="15"/>
-      <c r="W73" s="15"/>
+        <v/>
+      </c>
+      <c r="S73" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T73" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="U73" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V73" s="16"/>
+      <c r="W73" s="16"/>
       <c r="X73" s="16" t="s">
         <v>40</v>
       </c>
@@ -9232,7 +8637,7 @@
       <c r="AE73" s="15"/>
       <c r="AF73" s="15"/>
     </row>
-    <row r="74" customHeight="1" spans="1:32">
+    <row r="74" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>151</v>
       </c>
@@ -9251,7 +8656,7 @@
       <c r="F74" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="G74" s="6" t="s">
+      <c r="G74" s="8" t="s">
         <v>369</v>
       </c>
       <c r="H74" s="6" t="s">
@@ -9272,13 +8677,13 @@
       <c r="M74" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="N74" s="6" t="s">
+      <c r="N74" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="O74" s="6" t="s">
+      <c r="O74" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="P74" s="6" t="s">
+      <c r="P74" s="8" t="s">
         <v>419</v>
       </c>
       <c r="Q74" s="6" t="s">
@@ -9286,15 +8691,15 @@
       </c>
       <c r="R74" s="8" t="str" cm="1">
         <f t="array" ref="R74">_xlfn.LET(_xlpm.issn,TRIM(M74),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.1</v>
-      </c>
-      <c r="S74" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
-      <c r="V74" s="6"/>
-      <c r="W74" s="6"/>
+        <v/>
+      </c>
+      <c r="S74" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T74" s="8"/>
+      <c r="U74" s="8"/>
+      <c r="V74" s="8"/>
+      <c r="W74" s="8"/>
       <c r="X74" s="8" t="s">
         <v>40</v>
       </c>
@@ -9311,7 +8716,7 @@
       <c r="AE74" s="6"/>
       <c r="AF74" s="6"/>
     </row>
-    <row r="75" customHeight="1" spans="1:32">
+    <row r="75" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="15" t="s">
         <v>421</v>
       </c>
@@ -9330,7 +8735,7 @@
       <c r="F75" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="G75" s="15" t="s">
+      <c r="G75" s="16" t="s">
         <v>393</v>
       </c>
       <c r="H75" s="15" t="s">
@@ -9349,11 +8754,11 @@
         <v>the 14th International FLINS Conference on Robotics and Artificial Intelligence (FLINS 2020)</v>
       </c>
       <c r="M75" s="15"/>
-      <c r="N75" s="15"/>
-      <c r="O75" s="15" t="s">
+      <c r="N75" s="16"/>
+      <c r="O75" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P75" s="15" t="s">
+      <c r="P75" s="16" t="s">
         <v>424</v>
       </c>
       <c r="Q75" s="15" t="s">
@@ -9363,15 +8768,15 @@
         <f t="array" ref="R75">_xlfn.LET(_xlpm.issn,TRIM(M75),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S75" s="15"/>
-      <c r="T75" s="15"/>
-      <c r="U75" s="15"/>
-      <c r="V75" s="15"/>
-      <c r="W75" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="X75" s="15"/>
-      <c r="Y75" s="15"/>
+      <c r="S75" s="16"/>
+      <c r="T75" s="16"/>
+      <c r="U75" s="16"/>
+      <c r="V75" s="16"/>
+      <c r="W75" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X75" s="16"/>
+      <c r="Y75" s="16"/>
       <c r="Z75" s="15"/>
       <c r="AA75" s="15"/>
       <c r="AB75" s="15"/>
@@ -9384,7 +8789,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="1:32">
+    <row r="76" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>151</v>
       </c>
@@ -9403,7 +8808,7 @@
       <c r="F76" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="G76" s="6" t="s">
+      <c r="G76" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H76" s="6" t="s">
@@ -9424,13 +8829,13 @@
       <c r="M76" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="N76" s="6" t="s">
+      <c r="N76" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="O76" s="6" t="s">
+      <c r="O76" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P76" s="6" t="s">
+      <c r="P76" s="8" t="s">
         <v>433</v>
       </c>
       <c r="Q76" s="6" t="s">
@@ -9438,17 +8843,17 @@
       </c>
       <c r="R76" s="8" t="str" cm="1">
         <f t="array" ref="R76">_xlfn.LET(_xlpm.issn,TRIM(M76),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>8.0</v>
-      </c>
-      <c r="S76" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
+        <v/>
+      </c>
+      <c r="S76" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T76" s="8"/>
+      <c r="U76" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V76" s="8"/>
+      <c r="W76" s="8"/>
       <c r="X76" s="8"/>
       <c r="Y76" s="8"/>
       <c r="Z76" s="6" t="s">
@@ -9461,7 +8866,7 @@
       <c r="AE76" s="6"/>
       <c r="AF76" s="6"/>
     </row>
-    <row r="77" customHeight="1" spans="1:32">
+    <row r="77" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="15" t="s">
         <v>151</v>
       </c>
@@ -9480,7 +8885,7 @@
       <c r="F77" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="G77" s="15" t="s">
+      <c r="G77" s="16" t="s">
         <v>393</v>
       </c>
       <c r="H77" s="15" t="s">
@@ -9501,13 +8906,13 @@
       <c r="M77" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="N77" s="15" t="s">
+      <c r="N77" s="16" t="s">
         <v>437</v>
       </c>
-      <c r="O77" s="15" t="s">
+      <c r="O77" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="P77" s="15" t="s">
+      <c r="P77" s="16" t="s">
         <v>438</v>
       </c>
       <c r="Q77" s="15" t="s">
@@ -9515,17 +8920,17 @@
       </c>
       <c r="R77" s="8" t="str" cm="1">
         <f t="array" ref="R77">_xlfn.LET(_xlpm.issn,TRIM(M77),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>10.2</v>
-      </c>
-      <c r="S77" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T77" s="15"/>
-      <c r="U77" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V77" s="15"/>
-      <c r="W77" s="15"/>
+        <v/>
+      </c>
+      <c r="S77" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T77" s="16"/>
+      <c r="U77" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V77" s="16"/>
+      <c r="W77" s="16"/>
       <c r="X77" s="16"/>
       <c r="Y77" s="16"/>
       <c r="Z77" s="15" t="s">
@@ -9540,7 +8945,7 @@
       <c r="AE77" s="15"/>
       <c r="AF77" s="15"/>
     </row>
-    <row r="78" customHeight="1" spans="1:32">
+    <row r="78" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>421</v>
       </c>
@@ -9559,7 +8964,7 @@
       <c r="F78" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="G78" s="6" t="s">
+      <c r="G78" s="8" t="s">
         <v>441</v>
       </c>
       <c r="H78" s="6" t="s">
@@ -9578,13 +8983,13 @@
         <v>the 14th International Conference on Intelligent Systems and Knowledge Engineering (ISKE)</v>
       </c>
       <c r="M78" s="6"/>
-      <c r="N78" s="6" t="s">
+      <c r="N78" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="O78" s="6" t="s">
+      <c r="O78" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P78" s="6" t="s">
+      <c r="P78" s="8" t="s">
         <v>444</v>
       </c>
       <c r="Q78" s="6" t="s">
@@ -9594,17 +8999,17 @@
         <f t="array" ref="R78">_xlfn.LET(_xlpm.issn,TRIM(M78),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V78" s="6"/>
-      <c r="W78" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="X78" s="6"/>
-      <c r="Y78" s="6"/>
+      <c r="S78" s="8"/>
+      <c r="T78" s="8"/>
+      <c r="U78" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V78" s="8"/>
+      <c r="W78" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="X78" s="8"/>
+      <c r="Y78" s="8"/>
       <c r="Z78" s="6"/>
       <c r="AA78" s="6"/>
       <c r="AB78" s="6"/>
@@ -9617,7 +9022,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="1:32">
+    <row r="79" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="15" t="s">
         <v>421</v>
       </c>
@@ -9636,7 +9041,7 @@
       <c r="F79" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="G79" s="15" t="s">
+      <c r="G79" s="16" t="s">
         <v>441</v>
       </c>
       <c r="H79" s="15" t="s">
@@ -9655,13 +9060,13 @@
         <v>the 14th International Conference on Intelligent Systems and Knowledge Engineering (ISKE)</v>
       </c>
       <c r="M79" s="15"/>
-      <c r="N79" s="15" t="s">
+      <c r="N79" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="O79" s="15" t="s">
+      <c r="O79" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P79" s="15" t="s">
+      <c r="P79" s="16" t="s">
         <v>450</v>
       </c>
       <c r="Q79" s="15" t="s">
@@ -9671,17 +9076,17 @@
         <f t="array" ref="R79">_xlfn.LET(_xlpm.issn,TRIM(M79),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S79" s="15"/>
-      <c r="T79" s="15"/>
-      <c r="U79" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V79" s="15"/>
-      <c r="W79" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="X79" s="15"/>
-      <c r="Y79" s="15"/>
+      <c r="S79" s="16"/>
+      <c r="T79" s="16"/>
+      <c r="U79" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V79" s="16"/>
+      <c r="W79" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X79" s="16"/>
+      <c r="Y79" s="16"/>
       <c r="Z79" s="15"/>
       <c r="AA79" s="15"/>
       <c r="AB79" s="15"/>
@@ -9694,7 +9099,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="1:32">
+    <row r="80" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>151</v>
       </c>
@@ -9713,7 +9118,7 @@
       <c r="F80" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="G80" s="6" t="s">
+      <c r="G80" s="8" t="s">
         <v>441</v>
       </c>
       <c r="H80" s="6" t="s">
@@ -9734,13 +9139,13 @@
       <c r="M80" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="N80" s="6" t="s">
+      <c r="N80" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="O80" s="6" t="s">
+      <c r="O80" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P80" s="6" t="s">
+      <c r="P80" s="8" t="s">
         <v>455</v>
       </c>
       <c r="Q80" s="6" t="s">
@@ -9748,19 +9153,19 @@
       </c>
       <c r="R80" s="8" t="str" cm="1">
         <f t="array" ref="R80">_xlfn.LET(_xlpm.issn,TRIM(M80),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.8</v>
-      </c>
-      <c r="S80" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T80" s="6" t="s">
+        <v/>
+      </c>
+      <c r="S80" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T80" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="U80" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V80" s="6"/>
-      <c r="W80" s="6"/>
+      <c r="U80" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V80" s="8"/>
+      <c r="W80" s="8"/>
       <c r="X80" s="8"/>
       <c r="Y80" s="8"/>
       <c r="Z80" s="6"/>
@@ -9771,7 +9176,7 @@
       <c r="AE80" s="6"/>
       <c r="AF80" s="6"/>
     </row>
-    <row r="81" customHeight="1" spans="1:32">
+    <row r="81" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="15" t="s">
         <v>421</v>
       </c>
@@ -9790,7 +9195,7 @@
       <c r="F81" s="15" t="s">
         <v>458</v>
       </c>
-      <c r="G81" s="15" t="s">
+      <c r="G81" s="16" t="s">
         <v>441</v>
       </c>
       <c r="H81" s="15" t="s">
@@ -9809,13 +9214,13 @@
         <v>the 11th Conference of the European Society for Fuzzy Logic and Technology (EUSFLAT 2019)</v>
       </c>
       <c r="M81" s="15"/>
-      <c r="N81" s="15" t="s">
+      <c r="N81" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="O81" s="15" t="s">
+      <c r="O81" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P81" s="15" t="s">
+      <c r="P81" s="16" t="s">
         <v>461</v>
       </c>
       <c r="Q81" s="15" t="s">
@@ -9825,17 +9230,17 @@
         <f t="array" ref="R81">_xlfn.LET(_xlpm.issn,TRIM(M81),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S81" s="15"/>
-      <c r="T81" s="15"/>
-      <c r="U81" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V81" s="15"/>
-      <c r="W81" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="X81" s="15"/>
-      <c r="Y81" s="15"/>
+      <c r="S81" s="16"/>
+      <c r="T81" s="16"/>
+      <c r="U81" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V81" s="16"/>
+      <c r="W81" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X81" s="16"/>
+      <c r="Y81" s="16"/>
       <c r="Z81" s="15"/>
       <c r="AA81" s="15"/>
       <c r="AB81" s="15"/>
@@ -9848,7 +9253,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="82" customHeight="1" spans="1:32">
+    <row r="82" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>151</v>
       </c>
@@ -9867,7 +9272,7 @@
       <c r="F82" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="G82" s="8" t="s">
         <v>467</v>
       </c>
       <c r="H82" s="6" t="s">
@@ -9888,13 +9293,13 @@
       <c r="M82" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="N82" s="6" t="s">
+      <c r="N82" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="O82" s="6" t="s">
+      <c r="O82" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P82" s="6" t="s">
+      <c r="P82" s="8" t="s">
         <v>470</v>
       </c>
       <c r="Q82" s="6" t="s">
@@ -9902,17 +9307,17 @@
       </c>
       <c r="R82" s="8" t="str" cm="1">
         <f t="array" ref="R82">_xlfn.LET(_xlpm.issn,TRIM(M82),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>6.0</v>
-      </c>
-      <c r="S82" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T82" s="6"/>
-      <c r="U82" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V82" s="6"/>
-      <c r="W82" s="6"/>
+        <v/>
+      </c>
+      <c r="S82" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T82" s="8"/>
+      <c r="U82" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V82" s="8"/>
+      <c r="W82" s="8"/>
       <c r="X82" s="8" t="s">
         <v>40</v>
       </c>
@@ -9925,7 +9330,7 @@
       <c r="AE82" s="6"/>
       <c r="AF82" s="6"/>
     </row>
-    <row r="83" customHeight="1" spans="1:32">
+    <row r="83" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="15" t="s">
         <v>421</v>
       </c>
@@ -9940,7 +9345,7 @@
       <c r="F83" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="G83" s="15" t="s">
+      <c r="G83" s="16" t="s">
         <v>467</v>
       </c>
       <c r="H83" s="15" t="s">
@@ -9959,13 +9364,13 @@
         <v>the 13th International FLINS Conference on Data Science and Knowledge Engineering for Sensing Decision Support (FLINS 2018)</v>
       </c>
       <c r="M83" s="15"/>
-      <c r="N83" s="15" t="s">
+      <c r="N83" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="O83" s="15" t="s">
+      <c r="O83" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P83" s="15" t="s">
+      <c r="P83" s="16" t="s">
         <v>474</v>
       </c>
       <c r="Q83" s="15" t="s">
@@ -9975,15 +9380,15 @@
         <f t="array" ref="R83">_xlfn.LET(_xlpm.issn,TRIM(M83),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S83" s="15"/>
-      <c r="T83" s="15"/>
-      <c r="U83" s="15"/>
-      <c r="V83" s="15"/>
-      <c r="W83" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="X83" s="15"/>
-      <c r="Y83" s="15"/>
+      <c r="S83" s="16"/>
+      <c r="T83" s="16"/>
+      <c r="U83" s="16"/>
+      <c r="V83" s="16"/>
+      <c r="W83" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X83" s="16"/>
+      <c r="Y83" s="16"/>
       <c r="Z83" s="15"/>
       <c r="AA83" s="15"/>
       <c r="AB83" s="15"/>
@@ -9996,7 +9401,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="1:32">
+    <row r="84" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>151</v>
       </c>
@@ -10015,7 +9420,7 @@
       <c r="F84" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="G84" s="6" t="s">
+      <c r="G84" s="8" t="s">
         <v>467</v>
       </c>
       <c r="H84" s="6" t="s">
@@ -10032,32 +9437,32 @@
         <v>482</v>
       </c>
       <c r="M84" s="6"/>
-      <c r="N84" s="6" t="s">
+      <c r="N84" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="O84" s="6" t="s">
+      <c r="O84" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="P84" s="6" t="s">
+      <c r="P84" s="8" t="s">
         <v>484</v>
       </c>
       <c r="Q84" s="6" t="s">
         <v>485</v>
       </c>
       <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V84" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="W84" s="6"/>
-      <c r="X84" s="6" t="s">
+      <c r="S84" s="8"/>
+      <c r="T84" s="8"/>
+      <c r="U84" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V84" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="W84" s="8"/>
+      <c r="X84" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="Y84" s="6"/>
+      <c r="Y84" s="8"/>
       <c r="Z84" s="6"/>
       <c r="AA84" s="6"/>
       <c r="AB84" s="6"/>
@@ -10066,7 +9471,7 @@
       <c r="AE84" s="6"/>
       <c r="AF84" s="6"/>
     </row>
-    <row r="85" customHeight="1" spans="1:32">
+    <row r="85" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="15" t="s">
         <v>151</v>
       </c>
@@ -10085,7 +9490,7 @@
       <c r="F85" s="15" t="s">
         <v>487</v>
       </c>
-      <c r="G85" s="15" t="s">
+      <c r="G85" s="16" t="s">
         <v>467</v>
       </c>
       <c r="H85" s="15" t="s">
@@ -10106,13 +9511,13 @@
       <c r="M85" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="N85" s="15" t="s">
+      <c r="N85" s="16" t="s">
         <v>489</v>
       </c>
-      <c r="O85" s="15" t="s">
+      <c r="O85" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P85" s="15" t="s">
+      <c r="P85" s="16" t="s">
         <v>490</v>
       </c>
       <c r="Q85" s="15" t="s">
@@ -10120,17 +9525,17 @@
       </c>
       <c r="R85" s="8" t="str" cm="1">
         <f t="array" ref="R85">_xlfn.LET(_xlpm.issn,TRIM(M85),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>9.4</v>
-      </c>
-      <c r="S85" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T85" s="15"/>
-      <c r="U85" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V85" s="15"/>
-      <c r="W85" s="15"/>
+        <v/>
+      </c>
+      <c r="S85" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T85" s="16"/>
+      <c r="U85" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V85" s="16"/>
+      <c r="W85" s="16"/>
       <c r="X85" s="16"/>
       <c r="Y85" s="16"/>
       <c r="Z85" s="15" t="s">
@@ -10143,7 +9548,7 @@
       <c r="AE85" s="15"/>
       <c r="AF85" s="15"/>
     </row>
-    <row r="86" customHeight="1" spans="1:32">
+    <row r="86" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>151</v>
       </c>
@@ -10162,7 +9567,7 @@
       <c r="F86" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="G86" s="6" t="s">
+      <c r="G86" s="8" t="s">
         <v>467</v>
       </c>
       <c r="H86" s="6" t="s">
@@ -10183,13 +9588,13 @@
       <c r="M86" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="N86" s="6" t="s">
+      <c r="N86" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="O86" s="6" t="s">
+      <c r="O86" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P86" s="6" t="s">
+      <c r="P86" s="8" t="s">
         <v>495</v>
       </c>
       <c r="Q86" s="6" t="s">
@@ -10197,17 +9602,17 @@
       </c>
       <c r="R86" s="8" t="str" cm="1">
         <f t="array" ref="R86">_xlfn.LET(_xlpm.issn,TRIM(M86),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>8.0</v>
-      </c>
-      <c r="S86" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T86" s="6"/>
-      <c r="U86" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V86" s="6"/>
-      <c r="W86" s="6"/>
+        <v/>
+      </c>
+      <c r="S86" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T86" s="8"/>
+      <c r="U86" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V86" s="8"/>
+      <c r="W86" s="8"/>
       <c r="X86" s="8"/>
       <c r="Y86" s="8"/>
       <c r="Z86" s="6" t="s">
@@ -10222,7 +9627,7 @@
       <c r="AE86" s="6"/>
       <c r="AF86" s="6"/>
     </row>
-    <row r="87" customHeight="1" spans="1:32">
+    <row r="87" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="15" t="s">
         <v>151</v>
       </c>
@@ -10241,7 +9646,7 @@
       <c r="F87" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="G87" s="15" t="s">
+      <c r="G87" s="16" t="s">
         <v>498</v>
       </c>
       <c r="H87" s="15" t="s">
@@ -10262,13 +9667,13 @@
       <c r="M87" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="N87" s="15" t="s">
+      <c r="N87" s="16" t="s">
         <v>500</v>
       </c>
-      <c r="O87" s="15" t="s">
+      <c r="O87" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P87" s="15" t="s">
+      <c r="P87" s="16" t="s">
         <v>501</v>
       </c>
       <c r="Q87" s="15" t="s">
@@ -10276,19 +9681,19 @@
       </c>
       <c r="R87" s="8" t="str" cm="1">
         <f t="array" ref="R87">_xlfn.LET(_xlpm.issn,TRIM(M87),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.3</v>
-      </c>
-      <c r="S87" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T87" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="U87" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V87" s="15"/>
-      <c r="W87" s="15"/>
+        <v/>
+      </c>
+      <c r="S87" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T87" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="U87" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V87" s="16"/>
+      <c r="W87" s="16"/>
       <c r="X87" s="16" t="s">
         <v>40</v>
       </c>
@@ -10305,7 +9710,7 @@
       <c r="AE87" s="15"/>
       <c r="AF87" s="15"/>
     </row>
-    <row r="88" customHeight="1" spans="1:32">
+    <row r="88" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>421</v>
       </c>
@@ -10320,7 +9725,7 @@
       <c r="F88" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="G88" s="6" t="s">
+      <c r="G88" s="8" t="s">
         <v>498</v>
       </c>
       <c r="H88" s="6" t="s">
@@ -10339,13 +9744,13 @@
         <v>the 12th International Conference on Intelligent Systems and Knowledge Engineering (ISKE2017)</v>
       </c>
       <c r="M88" s="6"/>
-      <c r="N88" s="6" t="s">
+      <c r="N88" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="O88" s="6" t="s">
+      <c r="O88" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P88" s="6" t="s">
+      <c r="P88" s="8" t="s">
         <v>506</v>
       </c>
       <c r="Q88" s="6" t="s">
@@ -10355,17 +9760,17 @@
         <f t="array" ref="R88">_xlfn.LET(_xlpm.issn,TRIM(M88),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S88" s="6"/>
-      <c r="T88" s="6"/>
-      <c r="U88" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V88" s="6"/>
-      <c r="W88" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="X88" s="6"/>
-      <c r="Y88" s="6"/>
+      <c r="S88" s="8"/>
+      <c r="T88" s="8"/>
+      <c r="U88" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V88" s="8"/>
+      <c r="W88" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="X88" s="8"/>
+      <c r="Y88" s="8"/>
       <c r="Z88" s="6"/>
       <c r="AA88" s="6"/>
       <c r="AB88" s="6"/>
@@ -10378,7 +9783,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="89" customHeight="1" spans="1:32">
+    <row r="89" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="15" t="s">
         <v>421</v>
       </c>
@@ -10393,7 +9798,7 @@
       <c r="F89" s="15" t="s">
         <v>510</v>
       </c>
-      <c r="G89" s="15" t="s">
+      <c r="G89" s="16" t="s">
         <v>498</v>
       </c>
       <c r="H89" s="15" t="s">
@@ -10412,13 +9817,13 @@
         <v>the 12th International Conference on Intelligent Systems and Knowledge Engineering (ISKE2017)</v>
       </c>
       <c r="M89" s="15"/>
-      <c r="N89" s="15" t="s">
+      <c r="N89" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="O89" s="15" t="s">
+      <c r="O89" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P89" s="15" t="s">
+      <c r="P89" s="16" t="s">
         <v>506</v>
       </c>
       <c r="Q89" s="15" t="s">
@@ -10428,17 +9833,17 @@
         <f t="array" ref="R89">_xlfn.LET(_xlpm.issn,TRIM(M89),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S89" s="15"/>
-      <c r="T89" s="15"/>
-      <c r="U89" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V89" s="15"/>
-      <c r="W89" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="X89" s="15"/>
-      <c r="Y89" s="15"/>
+      <c r="S89" s="16"/>
+      <c r="T89" s="16"/>
+      <c r="U89" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V89" s="16"/>
+      <c r="W89" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X89" s="16"/>
+      <c r="Y89" s="16"/>
       <c r="Z89" s="15"/>
       <c r="AA89" s="15"/>
       <c r="AB89" s="15"/>
@@ -10451,7 +9856,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="1:32">
+    <row r="90" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>421</v>
       </c>
@@ -10470,7 +9875,7 @@
       <c r="F90" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="G90" s="6" t="s">
+      <c r="G90" s="8" t="s">
         <v>498</v>
       </c>
       <c r="H90" s="6" t="s">
@@ -10489,13 +9894,13 @@
         <v>the 2017 IEEE International Conference on Fuzzy Systems (FUZZ-IEEE)</v>
       </c>
       <c r="M90" s="6"/>
-      <c r="N90" s="6" t="s">
+      <c r="N90" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="O90" s="6" t="s">
+      <c r="O90" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P90" s="6" t="s">
+      <c r="P90" s="8" t="s">
         <v>506</v>
       </c>
       <c r="Q90" s="6" t="s">
@@ -10505,17 +9910,17 @@
         <f t="array" ref="R90">_xlfn.LET(_xlpm.issn,TRIM(M90),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="X90" s="6"/>
-      <c r="Y90" s="6"/>
+      <c r="S90" s="8"/>
+      <c r="T90" s="8"/>
+      <c r="U90" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V90" s="8"/>
+      <c r="W90" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="X90" s="8"/>
+      <c r="Y90" s="8"/>
       <c r="Z90" s="6"/>
       <c r="AA90" s="6"/>
       <c r="AB90" s="6"/>
@@ -10528,7 +9933,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="91" customHeight="1" spans="1:32">
+    <row r="91" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="15" t="s">
         <v>151</v>
       </c>
@@ -10547,7 +9952,7 @@
       <c r="F91" s="15" t="s">
         <v>518</v>
       </c>
-      <c r="G91" s="15" t="s">
+      <c r="G91" s="16" t="s">
         <v>498</v>
       </c>
       <c r="H91" s="15" t="s">
@@ -10568,13 +9973,13 @@
       <c r="M91" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="N91" s="15" t="s">
+      <c r="N91" s="16" t="s">
         <v>520</v>
       </c>
-      <c r="O91" s="15" t="s">
+      <c r="O91" s="16" t="s">
         <v>521</v>
       </c>
-      <c r="P91" s="15" t="s">
+      <c r="P91" s="16" t="s">
         <v>522</v>
       </c>
       <c r="Q91" s="15" t="s">
@@ -10582,19 +9987,19 @@
       </c>
       <c r="R91" s="8" t="str" cm="1">
         <f t="array" ref="R91">_xlfn.LET(_xlpm.issn,TRIM(M91),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>2.6</v>
-      </c>
-      <c r="S91" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T91" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="U91" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V91" s="15"/>
-      <c r="W91" s="15"/>
+        <v/>
+      </c>
+      <c r="S91" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T91" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="U91" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V91" s="16"/>
+      <c r="W91" s="16"/>
       <c r="X91" s="16" t="s">
         <v>40</v>
       </c>
@@ -10609,7 +10014,7 @@
       <c r="AE91" s="15"/>
       <c r="AF91" s="15"/>
     </row>
-    <row r="92" customHeight="1" spans="1:32">
+    <row r="92" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>151</v>
       </c>
@@ -10624,7 +10029,7 @@
       <c r="F92" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="G92" s="6" t="s">
+      <c r="G92" s="8" t="s">
         <v>498</v>
       </c>
       <c r="H92" s="6" t="s">
@@ -10645,13 +10050,13 @@
       <c r="M92" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="N92" s="6" t="s">
+      <c r="N92" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="O92" s="6" t="s">
+      <c r="O92" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="P92" s="6" t="s">
+      <c r="P92" s="8" t="s">
         <v>527</v>
       </c>
       <c r="Q92" s="6" t="s">
@@ -10659,19 +10064,19 @@
       </c>
       <c r="R92" s="8" t="str" cm="1">
         <f t="array" ref="R92">_xlfn.LET(_xlpm.issn,TRIM(M92),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>8.4</v>
-      </c>
-      <c r="S92" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T92" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U92" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V92" s="6"/>
-      <c r="W92" s="6"/>
+        <v/>
+      </c>
+      <c r="S92" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T92" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U92" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V92" s="8"/>
+      <c r="W92" s="8"/>
       <c r="X92" s="8" t="s">
         <v>40</v>
       </c>
@@ -10688,7 +10093,7 @@
       <c r="AE92" s="6"/>
       <c r="AF92" s="6"/>
     </row>
-    <row r="93" customHeight="1" spans="1:32">
+    <row r="93" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="15" t="s">
         <v>421</v>
       </c>
@@ -10707,7 +10112,7 @@
       <c r="F93" s="15" t="s">
         <v>529</v>
       </c>
-      <c r="G93" s="15" t="s">
+      <c r="G93" s="16" t="s">
         <v>530</v>
       </c>
       <c r="H93" s="15" t="s">
@@ -10726,13 +10131,13 @@
         <v>the 17th International Symposium on Knowledge and Systems Sciences (KSS 2016)</v>
       </c>
       <c r="M93" s="15"/>
-      <c r="N93" s="15" t="s">
+      <c r="N93" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="O93" s="15" t="s">
+      <c r="O93" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P93" s="15" t="s">
+      <c r="P93" s="16" t="s">
         <v>533</v>
       </c>
       <c r="Q93" s="15" t="s">
@@ -10742,17 +10147,17 @@
         <f t="array" ref="R93">_xlfn.LET(_xlpm.issn,TRIM(M93),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S93" s="15"/>
-      <c r="T93" s="15"/>
-      <c r="U93" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V93" s="15"/>
-      <c r="W93" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="X93" s="15"/>
-      <c r="Y93" s="15"/>
+      <c r="S93" s="16"/>
+      <c r="T93" s="16"/>
+      <c r="U93" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V93" s="16"/>
+      <c r="W93" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X93" s="16"/>
+      <c r="Y93" s="16"/>
       <c r="Z93" s="15"/>
       <c r="AA93" s="15"/>
       <c r="AB93" s="15"/>
@@ -10765,7 +10170,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="94" customHeight="1" spans="1:32">
+    <row r="94" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
         <v>421</v>
       </c>
@@ -10780,7 +10185,7 @@
       <c r="F94" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="G94" s="6" t="s">
+      <c r="G94" s="8" t="s">
         <v>530</v>
       </c>
       <c r="H94" s="6" t="s">
@@ -10799,13 +10204,13 @@
         <v>the 2016 IEEE International Conference on Fuzzy Systems (FUZZ-IEEE)</v>
       </c>
       <c r="M94" s="6"/>
-      <c r="N94" s="6" t="s">
+      <c r="N94" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="O94" s="6" t="s">
+      <c r="O94" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P94" s="6" t="s">
+      <c r="P94" s="8" t="s">
         <v>539</v>
       </c>
       <c r="Q94" s="6" t="s">
@@ -10815,17 +10220,17 @@
         <f t="array" ref="R94">_xlfn.LET(_xlpm.issn,TRIM(M94),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V94" s="6"/>
-      <c r="W94" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="X94" s="6"/>
-      <c r="Y94" s="6"/>
+      <c r="S94" s="8"/>
+      <c r="T94" s="8"/>
+      <c r="U94" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V94" s="8"/>
+      <c r="W94" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="X94" s="8"/>
+      <c r="Y94" s="8"/>
       <c r="Z94" s="6"/>
       <c r="AA94" s="6"/>
       <c r="AB94" s="6"/>
@@ -10838,7 +10243,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="95" customHeight="1" spans="1:32">
+    <row r="95" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="15" t="s">
         <v>421</v>
       </c>
@@ -10857,7 +10262,7 @@
       <c r="F95" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="G95" s="15" t="s">
+      <c r="G95" s="16" t="s">
         <v>530</v>
       </c>
       <c r="H95" s="15" t="s">
@@ -10876,13 +10281,13 @@
         <v>the 2016 IEEE International Conference on Fuzzy Systems (FUZZ-IEEE)</v>
       </c>
       <c r="M95" s="15"/>
-      <c r="N95" s="15" t="s">
+      <c r="N95" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="O95" s="15" t="s">
+      <c r="O95" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P95" s="15" t="s">
+      <c r="P95" s="16" t="s">
         <v>544</v>
       </c>
       <c r="Q95" s="15" t="s">
@@ -10892,17 +10297,17 @@
         <f t="array" ref="R95">_xlfn.LET(_xlpm.issn,TRIM(M95),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S95" s="15"/>
-      <c r="T95" s="15"/>
-      <c r="U95" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V95" s="15"/>
-      <c r="W95" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="X95" s="15"/>
-      <c r="Y95" s="15"/>
+      <c r="S95" s="16"/>
+      <c r="T95" s="16"/>
+      <c r="U95" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V95" s="16"/>
+      <c r="W95" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X95" s="16"/>
+      <c r="Y95" s="16"/>
       <c r="Z95" s="15"/>
       <c r="AA95" s="15"/>
       <c r="AB95" s="15"/>
@@ -10915,7 +10320,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="1:32">
+    <row r="96" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
         <v>151</v>
       </c>
@@ -10934,7 +10339,7 @@
       <c r="F96" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="G96" s="6" t="s">
+      <c r="G96" s="8" t="s">
         <v>530</v>
       </c>
       <c r="H96" s="6" t="s">
@@ -10955,13 +10360,13 @@
       <c r="M96" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="N96" s="6" t="s">
+      <c r="N96" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="O96" s="6" t="s">
+      <c r="O96" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="P96" s="6" t="s">
+      <c r="P96" s="8" t="s">
         <v>547</v>
       </c>
       <c r="Q96" s="6" t="s">
@@ -10969,17 +10374,17 @@
       </c>
       <c r="R96" s="8" t="str" cm="1">
         <f t="array" ref="R96">_xlfn.LET(_xlpm.issn,TRIM(M96),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.0</v>
-      </c>
-      <c r="S96" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T96" s="6"/>
-      <c r="U96" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V96" s="6"/>
-      <c r="W96" s="6"/>
+        <v/>
+      </c>
+      <c r="S96" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T96" s="8"/>
+      <c r="U96" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V96" s="8"/>
+      <c r="W96" s="8"/>
       <c r="X96" s="8"/>
       <c r="Y96" s="8"/>
       <c r="Z96" s="6"/>
@@ -10990,7 +10395,7 @@
       <c r="AE96" s="6"/>
       <c r="AF96" s="6"/>
     </row>
-    <row r="97" customHeight="1" spans="1:32">
+    <row r="97" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="15" t="s">
         <v>151</v>
       </c>
@@ -11009,7 +10414,7 @@
       <c r="F97" s="15" t="s">
         <v>518</v>
       </c>
-      <c r="G97" s="15" t="s">
+      <c r="G97" s="16" t="s">
         <v>530</v>
       </c>
       <c r="H97" s="15" t="s">
@@ -11030,13 +10435,13 @@
       <c r="M97" s="15" t="s">
         <v>551</v>
       </c>
-      <c r="N97" s="15" t="s">
+      <c r="N97" s="16" t="s">
         <v>552</v>
       </c>
-      <c r="O97" s="15" t="s">
+      <c r="O97" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="P97" s="15" t="s">
+      <c r="P97" s="16" t="s">
         <v>553</v>
       </c>
       <c r="Q97" s="15" t="s">
@@ -11044,17 +10449,17 @@
       </c>
       <c r="R97" s="8" t="str" cm="1">
         <f t="array" ref="R97">_xlfn.LET(_xlpm.issn,TRIM(M97),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>5.5</v>
-      </c>
-      <c r="S97" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T97" s="15"/>
-      <c r="U97" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V97" s="15"/>
-      <c r="W97" s="15"/>
+        <v/>
+      </c>
+      <c r="S97" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T97" s="16"/>
+      <c r="U97" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V97" s="16"/>
+      <c r="W97" s="16"/>
       <c r="X97" s="16"/>
       <c r="Y97" s="16"/>
       <c r="Z97" s="15"/>
@@ -11065,7 +10470,7 @@
       <c r="AE97" s="15"/>
       <c r="AF97" s="15"/>
     </row>
-    <row r="98" customHeight="1" spans="1:32">
+    <row r="98" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>151</v>
       </c>
@@ -11084,7 +10489,7 @@
       <c r="F98" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="G98" s="6" t="s">
+      <c r="G98" s="8" t="s">
         <v>530</v>
       </c>
       <c r="H98" s="6" t="s">
@@ -11105,13 +10510,13 @@
       <c r="M98" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="N98" s="6" t="s">
+      <c r="N98" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="O98" s="6" t="s">
+      <c r="O98" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="P98" s="6" t="s">
+      <c r="P98" s="8" t="s">
         <v>559</v>
       </c>
       <c r="Q98" s="6" t="s">
@@ -11119,19 +10524,19 @@
       </c>
       <c r="R98" s="8" t="str" cm="1">
         <f t="array" ref="R98">_xlfn.LET(_xlpm.issn,TRIM(M98),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>3.2</v>
-      </c>
-      <c r="S98" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T98" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U98" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V98" s="6"/>
-      <c r="W98" s="6"/>
+        <v/>
+      </c>
+      <c r="S98" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T98" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U98" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V98" s="8"/>
+      <c r="W98" s="8"/>
       <c r="X98" s="8"/>
       <c r="Y98" s="8"/>
       <c r="Z98" s="6"/>
@@ -11142,7 +10547,7 @@
       <c r="AE98" s="6"/>
       <c r="AF98" s="6"/>
     </row>
-    <row r="99" customHeight="1" spans="1:32">
+    <row r="99" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="15" t="s">
         <v>421</v>
       </c>
@@ -11157,7 +10562,7 @@
       <c r="F99" s="15" t="s">
         <v>518</v>
       </c>
-      <c r="G99" s="15" t="s">
+      <c r="G99" s="16" t="s">
         <v>561</v>
       </c>
       <c r="H99" s="15" t="s">
@@ -11176,13 +10581,13 @@
         <v>the 2015 IEEE International Conference on Fuzzy Systems (FUZZ-IEEE)</v>
       </c>
       <c r="M99" s="15"/>
-      <c r="N99" s="15" t="s">
+      <c r="N99" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="O99" s="15" t="s">
+      <c r="O99" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P99" s="15" t="s">
+      <c r="P99" s="16" t="s">
         <v>564</v>
       </c>
       <c r="Q99" s="15" t="s">
@@ -11192,17 +10597,17 @@
         <f t="array" ref="R99">_xlfn.LET(_xlpm.issn,TRIM(M99),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S99" s="15"/>
-      <c r="T99" s="15"/>
-      <c r="U99" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V99" s="15"/>
-      <c r="W99" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="X99" s="15"/>
-      <c r="Y99" s="15"/>
+      <c r="S99" s="16"/>
+      <c r="T99" s="16"/>
+      <c r="U99" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V99" s="16"/>
+      <c r="W99" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X99" s="16"/>
+      <c r="Y99" s="16"/>
       <c r="Z99" s="15"/>
       <c r="AA99" s="15"/>
       <c r="AB99" s="15"/>
@@ -11215,7 +10620,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="1:32">
+    <row r="100" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>151</v>
       </c>
@@ -11234,7 +10639,7 @@
       <c r="F100" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="G100" s="6" t="s">
+      <c r="G100" s="8" t="s">
         <v>530</v>
       </c>
       <c r="H100" s="6" t="s">
@@ -11255,13 +10660,13 @@
       <c r="M100" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="N100" s="6" t="s">
+      <c r="N100" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="O100" s="6" t="s">
+      <c r="O100" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="P100" s="6" t="s">
+      <c r="P100" s="8" t="s">
         <v>571</v>
       </c>
       <c r="Q100" s="6" t="s">
@@ -11269,19 +10674,19 @@
       </c>
       <c r="R100" s="8" t="str" cm="1">
         <f t="array" ref="R100">_xlfn.LET(_xlpm.issn,TRIM(M100),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.3</v>
-      </c>
-      <c r="S100" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T100" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U100" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V100" s="6"/>
-      <c r="W100" s="6"/>
+        <v/>
+      </c>
+      <c r="S100" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T100" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U100" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V100" s="8"/>
+      <c r="W100" s="8"/>
       <c r="X100" s="8"/>
       <c r="Y100" s="8">
         <v>2</v>
@@ -11294,7 +10699,7 @@
       <c r="AE100" s="6"/>
       <c r="AF100" s="6"/>
     </row>
-    <row r="101" customHeight="1" spans="1:32">
+    <row r="101" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="15" t="s">
         <v>151</v>
       </c>
@@ -11313,7 +10718,7 @@
       <c r="F101" s="15" t="s">
         <v>573</v>
       </c>
-      <c r="G101" s="15" t="s">
+      <c r="G101" s="16" t="s">
         <v>574</v>
       </c>
       <c r="H101" s="15" t="s">
@@ -11334,13 +10739,13 @@
       <c r="M101" s="17" t="s">
         <v>577</v>
       </c>
-      <c r="N101" s="15" t="s">
+      <c r="N101" s="16" t="s">
         <v>578</v>
       </c>
-      <c r="O101" s="15" t="s">
+      <c r="O101" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P101" s="15" t="s">
+      <c r="P101" s="16" t="s">
         <v>579</v>
       </c>
       <c r="Q101" s="15" t="s">
@@ -11348,17 +10753,17 @@
       </c>
       <c r="R101" s="8" t="str" cm="1">
         <f t="array" ref="R101">_xlfn.LET(_xlpm.issn,TRIM(M101),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>3.3</v>
-      </c>
-      <c r="S101" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T101" s="15"/>
-      <c r="U101" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V101" s="15"/>
-      <c r="W101" s="15"/>
+        <v/>
+      </c>
+      <c r="S101" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T101" s="16"/>
+      <c r="U101" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V101" s="16"/>
+      <c r="W101" s="16"/>
       <c r="X101" s="16"/>
       <c r="Y101" s="16"/>
       <c r="Z101" s="15"/>
@@ -11369,7 +10774,7 @@
       <c r="AE101" s="15"/>
       <c r="AF101" s="15"/>
     </row>
-    <row r="102" customHeight="1" spans="1:32">
+    <row r="102" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>151</v>
       </c>
@@ -11388,7 +10793,7 @@
       <c r="F102" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="G102" s="6" t="s">
+      <c r="G102" s="8" t="s">
         <v>574</v>
       </c>
       <c r="H102" s="6" t="s">
@@ -11409,13 +10814,13 @@
       <c r="M102" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="N102" s="6" t="s">
+      <c r="N102" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="O102" s="6" t="s">
+      <c r="O102" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P102" s="6" t="s">
+      <c r="P102" s="8" t="s">
         <v>583</v>
       </c>
       <c r="Q102" s="6" t="s">
@@ -11423,17 +10828,17 @@
       </c>
       <c r="R102" s="8" t="str" cm="1">
         <f t="array" ref="R102">_xlfn.LET(_xlpm.issn,TRIM(M102),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>7.3</v>
-      </c>
-      <c r="S102" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
+        <v/>
+      </c>
+      <c r="S102" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T102" s="8"/>
+      <c r="U102" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V102" s="8"/>
+      <c r="W102" s="8"/>
       <c r="X102" s="8" t="s">
         <v>40</v>
       </c>
@@ -11448,7 +10853,7 @@
       <c r="AE102" s="6"/>
       <c r="AF102" s="6"/>
     </row>
-    <row r="103" customHeight="1" spans="1:32">
+    <row r="103" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
         <v>151</v>
       </c>
@@ -11467,7 +10872,7 @@
       <c r="F103" s="15" t="s">
         <v>518</v>
       </c>
-      <c r="G103" s="15" t="s">
+      <c r="G103" s="16" t="s">
         <v>574</v>
       </c>
       <c r="H103" s="15" t="s">
@@ -11488,13 +10893,13 @@
       <c r="M103" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="N103" s="15" t="s">
+      <c r="N103" s="16" t="s">
         <v>586</v>
       </c>
-      <c r="O103" s="15" t="s">
+      <c r="O103" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="P103" s="15" t="s">
+      <c r="P103" s="16" t="s">
         <v>588</v>
       </c>
       <c r="Q103" s="15" t="s">
@@ -11502,17 +10907,17 @@
       </c>
       <c r="R103" s="8" t="str" cm="1">
         <f t="array" ref="R103">_xlfn.LET(_xlpm.issn,TRIM(M103),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>4.0</v>
-      </c>
-      <c r="S103" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="T103" s="15"/>
-      <c r="U103" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V103" s="15"/>
-      <c r="W103" s="15"/>
+        <v/>
+      </c>
+      <c r="S103" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="T103" s="16"/>
+      <c r="U103" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V103" s="16"/>
+      <c r="W103" s="16"/>
       <c r="X103" s="16"/>
       <c r="Y103" s="16"/>
       <c r="Z103" s="15"/>
@@ -11523,7 +10928,7 @@
       <c r="AE103" s="15"/>
       <c r="AF103" s="15"/>
     </row>
-    <row r="104" customHeight="1" spans="1:32">
+    <row r="104" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>421</v>
       </c>
@@ -11538,7 +10943,7 @@
       <c r="F104" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="G104" s="6" t="s">
+      <c r="G104" s="8" t="s">
         <v>591</v>
       </c>
       <c r="H104" s="6" t="s">
@@ -11557,13 +10962,13 @@
         <v>the 8th conference of the Euro-pean Society for Fuzzy Logic and Technology (EUSFLAT 2013)</v>
       </c>
       <c r="M104" s="6"/>
-      <c r="N104" s="6" t="s">
+      <c r="N104" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="O104" s="6" t="s">
+      <c r="O104" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P104" s="6" t="s">
+      <c r="P104" s="8" t="s">
         <v>594</v>
       </c>
       <c r="Q104" s="6" t="s">
@@ -11573,17 +10978,17 @@
         <f t="array" ref="R104">_xlfn.LET(_xlpm.issn,TRIM(M104),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
-      <c r="S104" s="6"/>
-      <c r="T104" s="6"/>
-      <c r="U104" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V104" s="6"/>
-      <c r="W104" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="X104" s="6"/>
-      <c r="Y104" s="6"/>
+      <c r="S104" s="8"/>
+      <c r="T104" s="8"/>
+      <c r="U104" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V104" s="8"/>
+      <c r="W104" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="X104" s="8"/>
+      <c r="Y104" s="8"/>
       <c r="Z104" s="6"/>
       <c r="AA104" s="6"/>
       <c r="AB104" s="6"/>
@@ -11596,7 +11001,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="105" customHeight="1" spans="1:32">
+    <row r="105" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="15" t="s">
         <v>151</v>
       </c>
@@ -11615,7 +11020,7 @@
       <c r="F105" s="15" t="s">
         <v>518</v>
       </c>
-      <c r="G105" s="15" t="s">
+      <c r="G105" s="16" t="s">
         <v>600</v>
       </c>
       <c r="H105" s="15" t="s">
@@ -11632,28 +11037,28 @@
         <v>604</v>
       </c>
       <c r="M105" s="15"/>
-      <c r="N105" s="15" t="s">
+      <c r="N105" s="16" t="s">
         <v>353</v>
       </c>
-      <c r="O105" s="15" t="s">
+      <c r="O105" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="P105" s="15" t="s">
+      <c r="P105" s="16" t="s">
         <v>605</v>
       </c>
       <c r="Q105" s="15" t="s">
         <v>606</v>
       </c>
       <c r="R105" s="15"/>
-      <c r="S105" s="15"/>
-      <c r="T105" s="15"/>
-      <c r="U105" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V105" s="15"/>
-      <c r="W105" s="15"/>
-      <c r="X105" s="15"/>
-      <c r="Y105" s="15"/>
+      <c r="S105" s="16"/>
+      <c r="T105" s="16"/>
+      <c r="U105" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V105" s="16"/>
+      <c r="W105" s="16"/>
+      <c r="X105" s="16"/>
+      <c r="Y105" s="16"/>
       <c r="Z105" s="15"/>
       <c r="AA105" s="15"/>
       <c r="AB105" s="15"/>
@@ -11662,7 +11067,7 @@
       <c r="AE105" s="15"/>
       <c r="AF105" s="15"/>
     </row>
-    <row r="106" customHeight="1" spans="1:32">
+    <row r="106" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>151</v>
       </c>
@@ -11681,7 +11086,7 @@
       <c r="F106" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="G106" s="6" t="s">
+      <c r="G106" s="8" t="s">
         <v>600</v>
       </c>
       <c r="H106" s="6" t="s">
@@ -11702,13 +11107,13 @@
       <c r="M106" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="N106" s="6" t="s">
+      <c r="N106" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="O106" s="6" t="s">
+      <c r="O106" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P106" s="6" t="s">
+      <c r="P106" s="8" t="s">
         <v>611</v>
       </c>
       <c r="Q106" s="6" t="s">
@@ -11716,17 +11121,17 @@
       </c>
       <c r="R106" s="8" t="str" cm="1">
         <f t="array" ref="R106">_xlfn.LET(_xlpm.issn,TRIM(M106),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>8.0</v>
-      </c>
-      <c r="S106" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T106" s="6"/>
-      <c r="U106" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="V106" s="6"/>
-      <c r="W106" s="6"/>
+        <v/>
+      </c>
+      <c r="S106" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T106" s="8"/>
+      <c r="U106" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V106" s="8"/>
+      <c r="W106" s="8"/>
       <c r="X106" s="8"/>
       <c r="Y106" s="8"/>
       <c r="Z106" s="6"/>
@@ -11737,7 +11142,7 @@
       <c r="AE106" s="6"/>
       <c r="AF106" s="6"/>
     </row>
-    <row r="107" customHeight="1" spans="1:32">
+    <row r="107" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="15" t="s">
         <v>421</v>
       </c>
@@ -11756,7 +11161,7 @@
       <c r="F107" s="15" t="s">
         <v>615</v>
       </c>
-      <c r="G107" s="15" t="s">
+      <c r="G107" s="16" t="s">
         <v>616</v>
       </c>
       <c r="H107" s="15" t="s">
@@ -11772,31 +11177,31 @@
       </c>
       <c r="L107" s="6" t="str">
         <f>IF(B107="英文",K107,"")</f>
-        <v> the 11th International Workshop on Meta-synthesis and Complex Systems (MCS 2011)</v>
+        <v xml:space="preserve"> the 11th International Workshop on Meta-synthesis and Complex Systems (MCS 2011)</v>
       </c>
       <c r="M107" s="15"/>
-      <c r="N107" s="15" t="s">
+      <c r="N107" s="16" t="s">
         <v>619</v>
       </c>
-      <c r="O107" s="15" t="s">
+      <c r="O107" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="P107" s="15" t="s">
+      <c r="P107" s="16" t="s">
         <v>620</v>
       </c>
       <c r="Q107" s="15" t="s">
         <v>621</v>
       </c>
       <c r="R107" s="15"/>
-      <c r="S107" s="15"/>
-      <c r="T107" s="15"/>
-      <c r="U107" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V107" s="15"/>
-      <c r="W107" s="15"/>
-      <c r="X107" s="15"/>
-      <c r="Y107" s="15"/>
+      <c r="S107" s="16"/>
+      <c r="T107" s="16"/>
+      <c r="U107" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V107" s="16"/>
+      <c r="W107" s="16"/>
+      <c r="X107" s="16"/>
+      <c r="Y107" s="16"/>
       <c r="Z107" s="15"/>
       <c r="AA107" s="15"/>
       <c r="AB107" s="15"/>
@@ -11809,7 +11214,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="108" customHeight="1" spans="1:32">
+    <row r="108" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>151</v>
       </c>
@@ -11824,7 +11229,7 @@
       <c r="F108" s="6" t="s">
         <v>625</v>
       </c>
-      <c r="G108" s="6" t="s">
+      <c r="G108" s="8" t="s">
         <v>616</v>
       </c>
       <c r="H108" s="6" t="s">
@@ -11841,30 +11246,30 @@
         <v>629</v>
       </c>
       <c r="M108" s="6"/>
-      <c r="N108" s="6" t="s">
+      <c r="N108" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="O108" s="6" t="s">
+      <c r="O108" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="P108" s="6" t="s">
+      <c r="P108" s="8" t="s">
         <v>630</v>
       </c>
       <c r="Q108" s="6" t="s">
         <v>631</v>
       </c>
       <c r="R108" s="6"/>
-      <c r="S108" s="6"/>
-      <c r="T108" s="6"/>
-      <c r="U108" s="6"/>
-      <c r="V108" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="W108" s="6"/>
-      <c r="X108" s="6" t="s">
+      <c r="S108" s="8"/>
+      <c r="T108" s="8"/>
+      <c r="U108" s="8"/>
+      <c r="V108" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="W108" s="8"/>
+      <c r="X108" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="Y108" s="6"/>
+      <c r="Y108" s="8"/>
       <c r="Z108" s="6"/>
       <c r="AA108" s="6"/>
       <c r="AB108" s="6"/>
@@ -11873,7 +11278,7 @@
       <c r="AE108" s="6"/>
       <c r="AF108" s="6"/>
     </row>
-    <row r="109" customHeight="1" spans="1:32">
+    <row r="109" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="15" t="s">
         <v>151</v>
       </c>
@@ -11888,7 +11293,7 @@
       <c r="F109" s="15" t="s">
         <v>518</v>
       </c>
-      <c r="G109" s="15" t="s">
+      <c r="G109" s="16" t="s">
         <v>616</v>
       </c>
       <c r="H109" s="15" t="s">
@@ -11909,13 +11314,13 @@
       <c r="M109" s="15" t="s">
         <v>634</v>
       </c>
-      <c r="N109" s="15" t="s">
+      <c r="N109" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="O109" s="15" t="s">
+      <c r="O109" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="P109" s="15" t="s">
+      <c r="P109" s="16" t="s">
         <v>635</v>
       </c>
       <c r="Q109" s="15" t="s">
@@ -11923,13 +11328,13 @@
       </c>
       <c r="R109" s="8" t="str" cm="1">
         <f t="array" ref="R109">_xlfn.LET(_xlpm.issn,TRIM(M109),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
-        <v>0.6</v>
-      </c>
-      <c r="S109" s="15"/>
-      <c r="T109" s="15"/>
-      <c r="U109" s="15"/>
-      <c r="V109" s="15"/>
-      <c r="W109" s="15"/>
+        <v/>
+      </c>
+      <c r="S109" s="16"/>
+      <c r="T109" s="16"/>
+      <c r="U109" s="16"/>
+      <c r="V109" s="16"/>
+      <c r="W109" s="16"/>
       <c r="X109" s="16"/>
       <c r="Y109" s="16"/>
       <c r="Z109" s="15"/>
@@ -11940,7 +11345,7 @@
       <c r="AE109" s="15"/>
       <c r="AF109" s="15"/>
     </row>
-    <row r="110" customHeight="1" spans="1:32">
+    <row r="110" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
         <v>151</v>
       </c>
@@ -11959,7 +11364,7 @@
       <c r="F110" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="G110" s="6" t="s">
+      <c r="G110" s="8" t="s">
         <v>616</v>
       </c>
       <c r="H110" s="6" t="s">
@@ -11976,28 +11381,28 @@
         <v>642</v>
       </c>
       <c r="M110" s="6"/>
-      <c r="N110" s="6" t="s">
+      <c r="N110" s="8" t="s">
         <v>643</v>
       </c>
-      <c r="O110" s="6" t="s">
+      <c r="O110" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="P110" s="6" t="s">
+      <c r="P110" s="8" t="s">
         <v>644</v>
       </c>
       <c r="Q110" s="6" t="s">
         <v>645</v>
       </c>
       <c r="R110" s="6"/>
-      <c r="S110" s="6"/>
-      <c r="T110" s="6"/>
-      <c r="U110" s="6"/>
-      <c r="V110" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="W110" s="6"/>
-      <c r="X110" s="6"/>
-      <c r="Y110" s="6"/>
+      <c r="S110" s="8"/>
+      <c r="T110" s="8"/>
+      <c r="U110" s="8"/>
+      <c r="V110" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="W110" s="8"/>
+      <c r="X110" s="8"/>
+      <c r="Y110" s="8"/>
       <c r="Z110" s="6"/>
       <c r="AA110" s="6"/>
       <c r="AB110" s="6"/>
@@ -12006,7 +11411,7 @@
       <c r="AE110" s="6"/>
       <c r="AF110" s="6"/>
     </row>
-    <row r="111" customHeight="1" spans="1:32">
+    <row r="111" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="15" t="s">
         <v>151</v>
       </c>
@@ -12025,7 +11430,7 @@
       <c r="F111" s="15" t="s">
         <v>518</v>
       </c>
-      <c r="G111" s="15" t="s">
+      <c r="G111" s="16" t="s">
         <v>616</v>
       </c>
       <c r="H111" s="15" t="s">
@@ -12042,28 +11447,28 @@
         <v>650</v>
       </c>
       <c r="M111" s="15"/>
-      <c r="N111" s="15" t="s">
+      <c r="N111" s="16" t="s">
         <v>610</v>
       </c>
-      <c r="O111" s="15" t="s">
+      <c r="O111" s="16" t="s">
         <v>521</v>
       </c>
-      <c r="P111" s="15" t="s">
+      <c r="P111" s="16" t="s">
         <v>651</v>
       </c>
       <c r="Q111" s="15" t="s">
         <v>652</v>
       </c>
       <c r="R111" s="15"/>
-      <c r="S111" s="15"/>
-      <c r="T111" s="15"/>
-      <c r="U111" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V111" s="15"/>
-      <c r="W111" s="15"/>
-      <c r="X111" s="15"/>
-      <c r="Y111" s="15"/>
+      <c r="S111" s="16"/>
+      <c r="T111" s="16"/>
+      <c r="U111" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="V111" s="16"/>
+      <c r="W111" s="16"/>
+      <c r="X111" s="16"/>
+      <c r="Y111" s="16"/>
       <c r="Z111" s="15"/>
       <c r="AA111" s="15"/>
       <c r="AB111" s="15"/>
@@ -12072,7 +11477,7 @@
       <c r="AE111" s="15"/>
       <c r="AF111" s="15"/>
     </row>
-    <row r="112" customHeight="1" spans="1:32">
+    <row r="112" spans="1:32" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
         <v>421</v>
       </c>
@@ -12091,7 +11496,7 @@
       <c r="F112" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="G112" s="6" t="s">
+      <c r="G112" s="8" t="s">
         <v>653</v>
       </c>
       <c r="H112" s="6" t="s">
@@ -12110,22 +11515,22 @@
         <v>the 10th International Symposium on Knowledge and Systems Sciences (KSS 2009)</v>
       </c>
       <c r="M112" s="6"/>
-      <c r="N112" s="6" t="s">
+      <c r="N112" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="O112" s="6" t="s">
+      <c r="O112" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="P112" s="6"/>
+      <c r="P112" s="8"/>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
-      <c r="S112" s="6"/>
-      <c r="T112" s="6"/>
-      <c r="U112" s="6"/>
-      <c r="V112" s="6"/>
-      <c r="W112" s="6"/>
-      <c r="X112" s="6"/>
-      <c r="Y112" s="6"/>
+      <c r="S112" s="8"/>
+      <c r="T112" s="8"/>
+      <c r="U112" s="8"/>
+      <c r="V112" s="8"/>
+      <c r="W112" s="8"/>
+      <c r="X112" s="8"/>
+      <c r="Y112" s="8"/>
       <c r="Z112" s="6"/>
       <c r="AA112" s="6"/>
       <c r="AB112" s="6"/>
@@ -12138,52 +11543,50 @@
         <v>657</v>
       </c>
     </row>
-    <row r="113" customHeight="1" spans="18:18">
+    <row r="113" spans="18:18" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="R113" s="8" t="str" cm="1">
         <f t="array" ref="R113">_xlfn.LET(_xlpm.issn,TRIM(M113),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
     </row>
-    <row r="114" customHeight="1" spans="18:18">
+    <row r="114" spans="18:18" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="R114" s="8" t="str" cm="1">
         <f t="array" ref="R114">_xlfn.LET(_xlpm.issn,TRIM(M114),_xlpm.jcr_issn,[1]Category_Quartiles!$C$2:$C$33000,_xlpm.jcr_eissn,[1]Category_Quartiles!$D$2:$D$33000,_xlpm.jif,[1]Category_Quartiles!$P$2:$P$33000,IFERROR(_xlfn.XLOOKUP(TRUE,((_xlpm.issn&lt;&gt;"")*((_xlpm.issn=_xlpm.jcr_issn)+(_xlpm.issn=_xlpm.jcr_eissn)))&gt;0,_xlpm.jif,""),""))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AF114" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:AF114" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="R113:R114 A2:AF112">
-    <cfRule type="expression" dxfId="0" priority="43">
+    <cfRule type="expression" dxfId="4" priority="43">
       <formula>MOD(ROW(),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:AF150">
-    <cfRule type="expression" dxfId="1" priority="42">
+    <cfRule type="expression" dxfId="3" priority="42">
       <formula>MOD(ROW(),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:AF112 R113:R114">
+  <conditionalFormatting sqref="R113:R114 A3:AF112">
     <cfRule type="expression" dxfId="2" priority="18">
       <formula>MOD(ROW(),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AF152">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>IF(EVEN(A3),TRUE,IF(A3="白色",TRUE,FALSE))</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="0" priority="17">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>IF(EVEN(A3),TRUE,IF(A3="白色",TRUE,FALSE))</formula>
-    </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="Q33" r:id="rId1" display="10.1016/j.eswa.2026.131876"/>
-    <hyperlink ref="Q80" r:id="rId2" display="10.1016/j.asoc.2019.105730"/>
-    <hyperlink ref="Q86" r:id="rId3" display="10.1016/j.knosys.2017.12.010"/>
+    <hyperlink ref="Q33" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="Q80" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="Q86" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>